--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/МЕРКУРИЙ ПРОИЗВОДСТВО И ПАКЕТАЖ АД/МЕРКУРИЙ ПРОИЗВОДСТВО И ПАКЕТАЖ АД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/МЕРКУРИЙ ПРОИЗВОДСТВО И ПАКЕТАЖ АД/МЕРКУРИЙ ПРОИЗВОДСТВО И ПАКЕТАЖ АД.xlsx
@@ -599,7 +599,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -609,12 +609,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -665,17 +659,17 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/МЕРКУРИЙ ПРОИЗВОДСТВО И ПАКЕТАЖ АД/МЕРКУРИЙ ПРОИЗВОДСТВО И ПАКЕТАЖ АД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/МЕРКУРИЙ ПРОИЗВОДСТВО И ПАКЕТАЖ АД/МЕРКУРИЙ ПРОИЗВОДСТВО И ПАКЕТАЖ АД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="187">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,304 +52,511 @@
     <t>Час</t>
   </si>
   <si>
-    <t>Плевен Хр.Ботев</t>
-  </si>
-  <si>
-    <t>Севлиево</t>
-  </si>
-  <si>
-    <t>Варна Чайка</t>
-  </si>
-  <si>
-    <t>Пирдоп</t>
-  </si>
-  <si>
-    <t>Димитровград</t>
-  </si>
-  <si>
-    <t>Кресна</t>
-  </si>
-  <si>
-    <t>Варна</t>
-  </si>
-  <si>
-    <t>София Ботевградско шосе</t>
-  </si>
-  <si>
-    <t>Търговище</t>
-  </si>
-  <si>
-    <t>Своге</t>
-  </si>
-  <si>
-    <t>Пловдив България</t>
-  </si>
-  <si>
-    <t>София Каменоделска</t>
-  </si>
-  <si>
-    <t>София Младост</t>
-  </si>
-  <si>
-    <t>Стара Загора</t>
-  </si>
-  <si>
-    <t>Добрич Добруджа</t>
-  </si>
-  <si>
-    <t>Русе Липник</t>
-  </si>
-  <si>
-    <t>Русе Дружба</t>
-  </si>
-  <si>
-    <t>В.Търново</t>
-  </si>
-  <si>
-    <t>Пловдив Цариградско шосе</t>
-  </si>
-  <si>
-    <t>Благоевград</t>
-  </si>
-  <si>
-    <t>Пловдив Бялата воденица</t>
-  </si>
-  <si>
-    <t>Монтана</t>
+    <t>Километри</t>
+  </si>
+  <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
+    <t>1124 Плевен Христо Ботев</t>
+  </si>
+  <si>
+    <t>1133 Кресна Е 79</t>
+  </si>
+  <si>
+    <t>1136 Димитровград Д. Благоев</t>
+  </si>
+  <si>
+    <t>1158 Варна Чайка</t>
+  </si>
+  <si>
+    <t>1163 София Ботевградско шосе</t>
+  </si>
+  <si>
+    <t>1186 Севлиево</t>
+  </si>
+  <si>
+    <t>1199 Varna Car Osvoboditel</t>
+  </si>
+  <si>
+    <t>1927 Пирдоп</t>
+  </si>
+  <si>
+    <t>1166 Своге</t>
+  </si>
+  <si>
+    <t>1918 O5 Търговище</t>
+  </si>
+  <si>
+    <t>1102 Стара Загора вход</t>
+  </si>
+  <si>
+    <t>1151 Пловдив, бул. България</t>
+  </si>
+  <si>
+    <t>1156 Добрич бул. Добруджа</t>
+  </si>
+  <si>
+    <t>1179 Русе, Липник</t>
+  </si>
+  <si>
+    <t>1182 София Каменоделска</t>
+  </si>
+  <si>
+    <t>1901 София, Младост 4-ти км</t>
+  </si>
+  <si>
+    <t>1103 Велико Търново изход</t>
+  </si>
+  <si>
+    <t>1172 Русе Шелф</t>
+  </si>
+  <si>
+    <t>1127 Благоевград</t>
+  </si>
+  <si>
+    <t>1144 Пловдив Стамболийски</t>
+  </si>
+  <si>
+    <t>1907 О5 Пловдив</t>
+  </si>
+  <si>
+    <t>1134 Монтана</t>
+  </si>
+  <si>
+    <t>1902 София, О5 Малинова Долина</t>
   </si>
   <si>
     <t>BT6273KP</t>
   </si>
   <si>
+    <t>BT6270KP</t>
+  </si>
+  <si>
+    <t>BT7814KT</t>
+  </si>
+  <si>
+    <t>BT6272KP</t>
+  </si>
+  <si>
+    <t>MPP1</t>
+  </si>
+  <si>
     <t>EB5362BB</t>
   </si>
   <si>
-    <t>BT6272KP</t>
+    <t>EB1778BA</t>
   </si>
   <si>
     <t>EB5026BP</t>
   </si>
   <si>
-    <t>BT7814KT</t>
-  </si>
-  <si>
-    <t>BT6270KP</t>
-  </si>
-  <si>
-    <t>EB1778BA</t>
-  </si>
-  <si>
-    <t>MPP1</t>
-  </si>
-  <si>
     <t>BT6269KP</t>
   </si>
   <si>
+    <t>EB7210BA</t>
+  </si>
+  <si>
     <t>EB2145AT</t>
   </si>
   <si>
-    <t>EB7210BA</t>
-  </si>
-  <si>
     <t>EB4092AX</t>
   </si>
   <si>
+    <t>EB3426BB</t>
+  </si>
+  <si>
     <t>MPP2</t>
   </si>
   <si>
     <t>BT7800KT</t>
   </si>
   <si>
-    <t>EB3426BB</t>
+    <t>EB2407BB</t>
   </si>
   <si>
     <t>BT6271KP</t>
   </si>
   <si>
-    <t>EB2407BB</t>
-  </si>
-  <si>
     <t>BT7796KT</t>
   </si>
   <si>
+    <t>EB5143BB</t>
+  </si>
+  <si>
     <t>EB1481BA</t>
   </si>
   <si>
-    <t>EB5143BB</t>
-  </si>
-  <si>
     <t>BT6267KP</t>
   </si>
   <si>
+    <t>BT7795KT</t>
+  </si>
+  <si>
     <t>78970154027720397</t>
   </si>
   <si>
+    <t>78970154027720363</t>
+  </si>
+  <si>
+    <t>78970154027720611</t>
+  </si>
+  <si>
+    <t>78970154027720389</t>
+  </si>
+  <si>
+    <t>78970154027720702</t>
+  </si>
+  <si>
     <t>78970154027720454</t>
   </si>
   <si>
-    <t>78970154027720389</t>
+    <t>78970154027720504</t>
   </si>
   <si>
     <t>78970154027720421</t>
   </si>
   <si>
-    <t>78970154027720611</t>
-  </si>
-  <si>
-    <t>78970154027720363</t>
-  </si>
-  <si>
-    <t>78970154027720504</t>
-  </si>
-  <si>
-    <t>78970154027720702</t>
-  </si>
-  <si>
     <t>78970154027720355</t>
   </si>
   <si>
+    <t>78970154027720686</t>
+  </si>
+  <si>
     <t>78970154027720439</t>
   </si>
   <si>
-    <t>78970154027720686</t>
-  </si>
-  <si>
     <t>78970154027720553</t>
   </si>
   <si>
+    <t>78970154027720660</t>
+  </si>
+  <si>
     <t>78970154027720710</t>
   </si>
   <si>
     <t>78970154027720603</t>
   </si>
   <si>
-    <t>78970154027720660</t>
+    <t>78970154027720645</t>
   </si>
   <si>
     <t>78970154027720371</t>
   </si>
   <si>
-    <t>78970154027720645</t>
-  </si>
-  <si>
     <t>78970154027720587</t>
   </si>
   <si>
+    <t>78970154027720678</t>
+  </si>
+  <si>
     <t>78970154027720496</t>
   </si>
   <si>
-    <t>78970154027720678</t>
-  </si>
-  <si>
     <t>78970154027720348</t>
   </si>
   <si>
+    <t>78970154027720579</t>
+  </si>
+  <si>
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
+    <t>30ML PERFUME AREON BLACK CRYSTAL</t>
+  </si>
+  <si>
     <t>ADBLUE 1L</t>
   </si>
   <si>
-    <t>30MЛ ПAPФЮM APEOH ЧEPEH KPИCTAЛ</t>
-  </si>
-  <si>
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>2026-06-16 04:39:12</t>
-  </si>
-  <si>
-    <t>2026-06-16 10:24:22</t>
-  </si>
-  <si>
-    <t>2026-06-16 13:40:30</t>
-  </si>
-  <si>
-    <t>2026-06-16 14:10:06</t>
-  </si>
-  <si>
-    <t>2026-06-16 14:11:33</t>
-  </si>
-  <si>
-    <t>2026-06-16 14:45:42</t>
-  </si>
-  <si>
-    <t>2026-06-16 14:45:43</t>
-  </si>
-  <si>
-    <t>2026-06-16 16:01:51</t>
-  </si>
-  <si>
-    <t>2026-06-16 16:18:08</t>
-  </si>
-  <si>
-    <t>2026-06-16 17:06:38</t>
-  </si>
-  <si>
-    <t>2026-06-17 09:27:35</t>
-  </si>
-  <si>
-    <t>2026-06-17 13:08:33</t>
-  </si>
-  <si>
-    <t>2026-06-17 14:09:36</t>
-  </si>
-  <si>
-    <t>2026-06-18 08:08:23</t>
-  </si>
-  <si>
-    <t>2026-06-18 08:49:10</t>
-  </si>
-  <si>
-    <t>2026-06-18 08:58:12</t>
-  </si>
-  <si>
-    <t>2026-06-18 09:25:45</t>
-  </si>
-  <si>
-    <t>2026-06-18 09:31:26</t>
-  </si>
-  <si>
-    <t>2026-06-18 10:38:56</t>
-  </si>
-  <si>
-    <t>2026-06-19 09:59:07</t>
-  </si>
-  <si>
-    <t>2026-06-19 10:46:57</t>
-  </si>
-  <si>
-    <t>2026-06-19 12:22:25</t>
-  </si>
-  <si>
-    <t>2026-06-22 10:47:52</t>
-  </si>
-  <si>
-    <t>2026-06-23 06:41:35</t>
-  </si>
-  <si>
-    <t>2026-06-23 08:16:58</t>
-  </si>
-  <si>
-    <t>2026-06-23 08:59:31</t>
-  </si>
-  <si>
-    <t>2026-06-23 09:37:06</t>
-  </si>
-  <si>
-    <t>2026-06-23 13:59:27</t>
-  </si>
-  <si>
-    <t>2026-06-24 08:22:26</t>
-  </si>
-  <si>
-    <t>2026-06-24 12:38:03</t>
-  </si>
-  <si>
-    <t>2026-06-25 09:17:45</t>
-  </si>
-  <si>
-    <t>2026-06-25 10:08:13</t>
+    <t>DIESEL DOUBLE FILTERED</t>
+  </si>
+  <si>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>PC</t>
+  </si>
+  <si>
+    <t>04:39:00</t>
+  </si>
+  <si>
+    <t>16:02:00</t>
+  </si>
+  <si>
+    <t>14:43:00</t>
+  </si>
+  <si>
+    <t>13:40:00</t>
+  </si>
+  <si>
+    <t>17:06:00</t>
+  </si>
+  <si>
+    <t>10:24:00</t>
+  </si>
+  <si>
+    <t>16:18:00</t>
+  </si>
+  <si>
+    <t>14:06:00</t>
+  </si>
+  <si>
+    <t>14:07:00</t>
+  </si>
+  <si>
+    <t>09:25:00</t>
+  </si>
+  <si>
+    <t>14:08:00</t>
+  </si>
+  <si>
+    <t>13:08:00</t>
+  </si>
+  <si>
+    <t>08:07:00</t>
+  </si>
+  <si>
+    <t>09:31:00</t>
+  </si>
+  <si>
+    <t>10:38:00</t>
+  </si>
+  <si>
+    <t>08:49:00</t>
+  </si>
+  <si>
+    <t>08:55:00</t>
+  </si>
+  <si>
+    <t>12:23:00</t>
+  </si>
+  <si>
+    <t>09:59:00</t>
+  </si>
+  <si>
+    <t>10:46:00</t>
+  </si>
+  <si>
+    <t>10:45:00</t>
+  </si>
+  <si>
+    <t>06:41:00</t>
+  </si>
+  <si>
+    <t>08:59:00</t>
+  </si>
+  <si>
+    <t>09:36:00</t>
+  </si>
+  <si>
+    <t>13:59:00</t>
+  </si>
+  <si>
+    <t>08:17:00</t>
+  </si>
+  <si>
+    <t>12:37:00</t>
+  </si>
+  <si>
+    <t>08:22:00</t>
+  </si>
+  <si>
+    <t>10:09:00</t>
+  </si>
+  <si>
+    <t>09:17:00</t>
+  </si>
+  <si>
+    <t>16:23:00</t>
+  </si>
+  <si>
+    <t>08:10:00</t>
+  </si>
+  <si>
+    <t>09:29:00</t>
+  </si>
+  <si>
+    <t>15:06:00</t>
+  </si>
+  <si>
+    <t>13:12:00</t>
+  </si>
+  <si>
+    <t>11:43:00</t>
+  </si>
+  <si>
+    <t>16:11:00</t>
+  </si>
+  <si>
+    <t>14:52:00</t>
+  </si>
+  <si>
+    <t>12:44:00</t>
+  </si>
+  <si>
+    <t>16:40:00</t>
+  </si>
+  <si>
+    <t>17:40:00</t>
+  </si>
+  <si>
+    <t>13:56:00</t>
+  </si>
+  <si>
+    <t>16:01:00</t>
+  </si>
+  <si>
+    <t>10:43:00</t>
+  </si>
+  <si>
+    <t>09:12:00</t>
+  </si>
+  <si>
+    <t>16:07:00</t>
+  </si>
+  <si>
+    <t>3233426076 3233426076</t>
+  </si>
+  <si>
+    <t>3233436480 3233436480</t>
+  </si>
+  <si>
+    <t>3233439393 3233439393</t>
+  </si>
+  <si>
+    <t>3233436980 3233436980</t>
+  </si>
+  <si>
+    <t>3233437116 3233437116</t>
+  </si>
+  <si>
+    <t>3233437576 3233437576</t>
+  </si>
+  <si>
+    <t>3233449233 3233449233</t>
+  </si>
+  <si>
+    <t>3233432282 3233432282</t>
+  </si>
+  <si>
+    <t>3233440838 3233440838</t>
+  </si>
+  <si>
+    <t>3233482388 3233482388</t>
+  </si>
+  <si>
+    <t>3233489015 3233489015</t>
+  </si>
+  <si>
+    <t>3233484476 3233484476</t>
+  </si>
+  <si>
+    <t>3233534894 3233534894</t>
+  </si>
+  <si>
+    <t>3233533627 3233533627</t>
+  </si>
+  <si>
+    <t>3233523942 3233523942</t>
+  </si>
+  <si>
+    <t>3233531518 3233531518</t>
+  </si>
+  <si>
+    <t>3233531453 3233531453</t>
+  </si>
+  <si>
+    <t>3233525206 3233525206</t>
+  </si>
+  <si>
+    <t>3233574074 3233574074</t>
+  </si>
+  <si>
+    <t>3233585030 3233585030</t>
+  </si>
+  <si>
+    <t>3233585562 3233585562</t>
+  </si>
+  <si>
+    <t>3233713395 3233713395</t>
+  </si>
+  <si>
+    <t>3233758969 3233758969</t>
+  </si>
+  <si>
+    <t>3233764575 3233764575</t>
+  </si>
+  <si>
+    <t>3233786661 3233786661</t>
+  </si>
+  <si>
+    <t>3233760090 3233760090</t>
+  </si>
+  <si>
+    <t>3233769164 3233769164</t>
+  </si>
+  <si>
+    <t>3233801494 3233801494</t>
+  </si>
+  <si>
+    <t>3233811609 3233811609</t>
+  </si>
+  <si>
+    <t>3233855272 3233855272</t>
+  </si>
+  <si>
+    <t>3233834096 3233834096</t>
+  </si>
+  <si>
+    <t>3233935836 3233935836</t>
+  </si>
+  <si>
+    <t>3233931415 3233931415</t>
+  </si>
+  <si>
+    <t>3233956470 3233956470</t>
+  </si>
+  <si>
+    <t>3234075152 3234075152</t>
+  </si>
+  <si>
+    <t>3234053082 3234053082</t>
+  </si>
+  <si>
+    <t>3234062679 3234062679</t>
+  </si>
+  <si>
+    <t>3234063991 3234063991</t>
+  </si>
+  <si>
+    <t>3234110188 3234110188</t>
+  </si>
+  <si>
+    <t>3234107681 3234107681</t>
+  </si>
+  <si>
+    <t>3234118236 3234118236</t>
+  </si>
+  <si>
+    <t>3234107162 3234107162</t>
+  </si>
+  <si>
+    <t>3234114904 3234114904</t>
+  </si>
+  <si>
+    <t>3234117069 3234117069</t>
+  </si>
+  <si>
+    <t>3234105689 3234105689</t>
+  </si>
+  <si>
+    <t>3234111727 3234111727</t>
+  </si>
+  <si>
+    <t>3234101408 3234101408</t>
   </si>
   <si>
     <t>Общи литри по продукт / МЕРКУРИЙ ПРОИЗВОДСТВО И ПАКЕТАЖ АД</t>
@@ -766,7 +976,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K42"/>
+  <dimension ref="A1:N59"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -775,14 +985,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -816,1258 +1029,2279 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
         <v>46189</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E2" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F2">
         <v>32.43</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2">
         <v>1.54</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>49.94</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.59</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>51.56</v>
       </c>
-      <c r="K2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="L2" t="s">
+        <v>88</v>
+      </c>
+      <c r="M2">
+        <v>225600</v>
+      </c>
+      <c r="N2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="3">
         <v>46189</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D3" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E3" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F3">
-        <v>39</v>
-      </c>
-      <c r="G3" s="1">
+        <v>43.81</v>
+      </c>
+      <c r="G3" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3">
         <v>1.54</v>
       </c>
-      <c r="H3">
-        <v>60.06</v>
-      </c>
       <c r="I3" s="1">
-        <v>1.59</v>
+        <v>67.47</v>
       </c>
       <c r="J3">
-        <v>62.01</v>
-      </c>
-      <c r="K3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+        <v>1.61</v>
+      </c>
+      <c r="K3" s="1">
+        <v>70.53</v>
+      </c>
+      <c r="L3" t="s">
+        <v>89</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="3">
         <v>46189</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D4" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E4" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F4">
-        <v>38</v>
-      </c>
-      <c r="G4" s="1">
+        <v>29.8</v>
+      </c>
+      <c r="G4" t="s">
+        <v>86</v>
+      </c>
+      <c r="H4">
         <v>1.54</v>
       </c>
-      <c r="H4">
-        <v>58.52</v>
-      </c>
       <c r="I4" s="1">
+        <v>45.89</v>
+      </c>
+      <c r="J4">
         <v>1.59</v>
       </c>
-      <c r="J4">
-        <v>60.42</v>
-      </c>
-      <c r="K4" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="K4" s="1">
+        <v>47.38</v>
+      </c>
+      <c r="L4" t="s">
+        <v>90</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="3">
         <v>46189</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D5" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E5" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="F5">
-        <v>64.61</v>
-      </c>
-      <c r="G5" s="1">
-        <v>1.54</v>
+        <v>1</v>
+      </c>
+      <c r="G5" t="s">
+        <v>87</v>
       </c>
       <c r="H5">
-        <v>99.5</v>
+        <v>3.52</v>
       </c>
       <c r="I5" s="1">
-        <v>1.59</v>
+        <v>3.52</v>
       </c>
       <c r="J5">
-        <v>102.73</v>
-      </c>
-      <c r="K5" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+        <v>3.52</v>
+      </c>
+      <c r="K5" s="1">
+        <v>3.52</v>
+      </c>
+      <c r="L5" t="s">
+        <v>90</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" s="3">
         <v>46189</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E6" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="F6">
-        <v>15.52</v>
-      </c>
-      <c r="G6" s="1">
-        <v>1.17</v>
+        <v>38</v>
+      </c>
+      <c r="G6" t="s">
+        <v>86</v>
       </c>
       <c r="H6">
-        <v>18.16</v>
+        <v>1.54</v>
       </c>
       <c r="I6" s="1">
-        <v>1.17</v>
+        <v>58.52</v>
       </c>
       <c r="J6">
-        <v>18.16</v>
-      </c>
-      <c r="K6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
+        <v>1.59</v>
+      </c>
+      <c r="K6" s="1">
+        <v>60.42</v>
+      </c>
+      <c r="L6" t="s">
+        <v>91</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" s="3">
         <v>46189</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D7" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E7" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F7">
-        <v>1</v>
-      </c>
-      <c r="G7" s="1">
-        <v>3.52</v>
+        <v>54.08</v>
+      </c>
+      <c r="G7" t="s">
+        <v>86</v>
       </c>
       <c r="H7">
-        <v>3.52</v>
+        <v>1.54</v>
       </c>
       <c r="I7" s="1">
-        <v>3.52</v>
+        <v>83.28</v>
       </c>
       <c r="J7">
-        <v>3.52</v>
-      </c>
-      <c r="K7" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
+        <v>1.59</v>
+      </c>
+      <c r="K7" s="1">
+        <v>85.98999999999999</v>
+      </c>
+      <c r="L7" t="s">
+        <v>92</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" s="3">
         <v>46189</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D8" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="E8" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F8">
-        <v>29.8</v>
-      </c>
-      <c r="G8" s="1">
+        <v>39</v>
+      </c>
+      <c r="G8" t="s">
+        <v>86</v>
+      </c>
+      <c r="H8">
         <v>1.54</v>
       </c>
-      <c r="H8">
-        <v>45.89</v>
-      </c>
       <c r="I8" s="1">
+        <v>60.06</v>
+      </c>
+      <c r="J8">
         <v>1.59</v>
       </c>
-      <c r="J8">
-        <v>47.38</v>
-      </c>
-      <c r="K8" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
+      <c r="K8" s="1">
+        <v>62.01</v>
+      </c>
+      <c r="L8" t="s">
+        <v>93</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" s="3">
         <v>46189</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D9" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="E9" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F9">
-        <v>43.81</v>
-      </c>
-      <c r="G9" s="1">
+        <v>39</v>
+      </c>
+      <c r="G9" t="s">
+        <v>86</v>
+      </c>
+      <c r="H9">
         <v>1.54</v>
       </c>
-      <c r="H9">
-        <v>67.47</v>
-      </c>
       <c r="I9" s="1">
-        <v>1.61</v>
+        <v>60.06</v>
       </c>
       <c r="J9">
-        <v>70.53</v>
-      </c>
-      <c r="K9" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
+        <v>1.59</v>
+      </c>
+      <c r="K9" s="1">
+        <v>62.01</v>
+      </c>
+      <c r="L9" t="s">
+        <v>94</v>
+      </c>
+      <c r="M9">
+        <v>415536</v>
+      </c>
+      <c r="N9" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" s="3">
         <v>46189</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="E10" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F10">
-        <v>39</v>
-      </c>
-      <c r="G10" s="1">
+        <v>64.61</v>
+      </c>
+      <c r="G10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H10">
         <v>1.54</v>
       </c>
-      <c r="H10">
-        <v>60.06</v>
-      </c>
       <c r="I10" s="1">
+        <v>99.5</v>
+      </c>
+      <c r="J10">
         <v>1.59</v>
       </c>
-      <c r="J10">
-        <v>62.01</v>
-      </c>
-      <c r="K10" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
+      <c r="K10" s="1">
+        <v>102.73</v>
+      </c>
+      <c r="L10" t="s">
+        <v>95</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" s="3">
         <v>46189</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D11" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E11" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="F11">
-        <v>54.08</v>
-      </c>
-      <c r="G11" s="1">
-        <v>1.54</v>
+        <v>15.52</v>
+      </c>
+      <c r="G11" t="s">
+        <v>86</v>
       </c>
       <c r="H11">
-        <v>83.28</v>
+        <v>1.17</v>
       </c>
       <c r="I11" s="1">
-        <v>1.59</v>
+        <v>18.16</v>
       </c>
       <c r="J11">
-        <v>85.98999999999999</v>
-      </c>
-      <c r="K11" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
+        <v>1.17</v>
+      </c>
+      <c r="K11" s="1">
+        <v>18.16</v>
+      </c>
+      <c r="L11" t="s">
+        <v>96</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" s="3">
         <v>46190</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D12" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E12" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F12">
         <v>46.39</v>
       </c>
-      <c r="G12" s="1">
+      <c r="G12" t="s">
+        <v>86</v>
+      </c>
+      <c r="H12">
         <v>1.53</v>
       </c>
-      <c r="H12">
+      <c r="I12" s="1">
         <v>70.98</v>
       </c>
-      <c r="I12" s="1">
+      <c r="J12">
         <v>1.59</v>
       </c>
-      <c r="J12">
+      <c r="K12" s="1">
         <v>73.76000000000001</v>
       </c>
-      <c r="K12" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
+      <c r="L12" t="s">
+        <v>97</v>
+      </c>
+      <c r="M12">
+        <v>234454</v>
+      </c>
+      <c r="N12" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" s="3">
         <v>46190</v>
       </c>
       <c r="B13" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C13" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D13" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="E13" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F13">
-        <v>46.32</v>
-      </c>
-      <c r="G13" s="1">
+        <v>50</v>
+      </c>
+      <c r="G13" t="s">
+        <v>86</v>
+      </c>
+      <c r="H13">
         <v>1.53</v>
       </c>
-      <c r="H13">
-        <v>70.87</v>
-      </c>
       <c r="I13" s="1">
+        <v>76.5</v>
+      </c>
+      <c r="J13">
         <v>1.59</v>
       </c>
-      <c r="J13">
-        <v>73.65000000000001</v>
-      </c>
-      <c r="K13" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
+      <c r="K13" s="1">
+        <v>79.5</v>
+      </c>
+      <c r="L13" t="s">
+        <v>98</v>
+      </c>
+      <c r="M13">
+        <v>573610</v>
+      </c>
+      <c r="N13" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" s="3">
         <v>46190</v>
       </c>
       <c r="B14" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C14" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D14" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E14" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F14">
-        <v>50</v>
-      </c>
-      <c r="G14" s="1">
+        <v>46.32</v>
+      </c>
+      <c r="G14" t="s">
+        <v>86</v>
+      </c>
+      <c r="H14">
         <v>1.53</v>
       </c>
-      <c r="H14">
-        <v>76.5</v>
-      </c>
       <c r="I14" s="1">
+        <v>70.87</v>
+      </c>
+      <c r="J14">
         <v>1.59</v>
       </c>
-      <c r="J14">
-        <v>79.5</v>
-      </c>
-      <c r="K14" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
+      <c r="K14" s="1">
+        <v>73.65000000000001</v>
+      </c>
+      <c r="L14" t="s">
+        <v>99</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" s="3">
         <v>46191</v>
       </c>
       <c r="B15" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C15" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E15" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F15">
-        <v>39.35</v>
-      </c>
-      <c r="G15" s="1">
-        <v>1.45</v>
+        <v>34.5</v>
+      </c>
+      <c r="G15" t="s">
+        <v>86</v>
       </c>
       <c r="H15">
-        <v>57.06</v>
+        <v>1.53</v>
       </c>
       <c r="I15" s="1">
-        <v>1.55</v>
+        <v>52.78</v>
       </c>
       <c r="J15">
-        <v>60.99</v>
-      </c>
-      <c r="K15" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
+        <v>1.58</v>
+      </c>
+      <c r="K15" s="1">
+        <v>54.51</v>
+      </c>
+      <c r="L15" t="s">
+        <v>97</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" s="3">
         <v>46191</v>
       </c>
       <c r="B16" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C16" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D16" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E16" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="F16">
-        <v>28.74</v>
-      </c>
-      <c r="G16" s="1">
+        <v>39.35</v>
+      </c>
+      <c r="G16" t="s">
+        <v>86</v>
+      </c>
+      <c r="H16">
         <v>1.45</v>
       </c>
-      <c r="H16">
-        <v>41.67</v>
-      </c>
       <c r="I16" s="1">
+        <v>57.06</v>
+      </c>
+      <c r="J16">
         <v>1.55</v>
       </c>
-      <c r="J16">
-        <v>44.55</v>
-      </c>
-      <c r="K16" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
+      <c r="K16" s="1">
+        <v>60.99</v>
+      </c>
+      <c r="L16" t="s">
+        <v>100</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" s="3">
         <v>46191</v>
       </c>
       <c r="B17" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C17" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D17" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="E17" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F17">
-        <v>40.69</v>
-      </c>
-      <c r="G17" s="1">
+        <v>58</v>
+      </c>
+      <c r="G17" t="s">
+        <v>86</v>
+      </c>
+      <c r="H17">
         <v>1.53</v>
       </c>
-      <c r="H17">
-        <v>62.26</v>
-      </c>
       <c r="I17" s="1">
-        <v>1.6</v>
+        <v>88.73999999999999</v>
       </c>
       <c r="J17">
-        <v>65.09999999999999</v>
-      </c>
-      <c r="K17" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
+        <v>1.58</v>
+      </c>
+      <c r="K17" s="1">
+        <v>91.64</v>
+      </c>
+      <c r="L17" t="s">
+        <v>101</v>
+      </c>
+      <c r="M17">
+        <v>388533</v>
+      </c>
+      <c r="N17" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18" s="3">
         <v>46191</v>
       </c>
       <c r="B18" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C18" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D18" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="E18" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F18">
-        <v>34.5</v>
-      </c>
-      <c r="G18" s="1">
+        <v>53.01</v>
+      </c>
+      <c r="G18" t="s">
+        <v>86</v>
+      </c>
+      <c r="H18">
         <v>1.53</v>
       </c>
-      <c r="H18">
-        <v>52.78</v>
-      </c>
       <c r="I18" s="1">
+        <v>81.11</v>
+      </c>
+      <c r="J18">
         <v>1.58</v>
       </c>
-      <c r="J18">
-        <v>54.51</v>
-      </c>
-      <c r="K18" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11">
+      <c r="K18" s="1">
+        <v>83.76000000000001</v>
+      </c>
+      <c r="L18" t="s">
+        <v>102</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
       <c r="A19" s="3">
         <v>46191</v>
       </c>
       <c r="B19" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C19" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D19" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E19" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="F19">
-        <v>58</v>
-      </c>
-      <c r="G19" s="1">
-        <v>1.53</v>
+        <v>28.74</v>
+      </c>
+      <c r="G19" t="s">
+        <v>86</v>
       </c>
       <c r="H19">
-        <v>88.73999999999999</v>
+        <v>1.45</v>
       </c>
       <c r="I19" s="1">
-        <v>1.58</v>
+        <v>41.67</v>
       </c>
       <c r="J19">
-        <v>91.64</v>
-      </c>
-      <c r="K19" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11">
+        <v>1.55</v>
+      </c>
+      <c r="K19" s="1">
+        <v>44.55</v>
+      </c>
+      <c r="L19" t="s">
+        <v>103</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
       <c r="A20" s="3">
         <v>46191</v>
       </c>
       <c r="B20" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C20" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="D20" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="E20" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F20">
-        <v>53.01</v>
-      </c>
-      <c r="G20" s="1">
+        <v>40.69</v>
+      </c>
+      <c r="G20" t="s">
+        <v>86</v>
+      </c>
+      <c r="H20">
         <v>1.53</v>
       </c>
-      <c r="H20">
-        <v>81.11</v>
-      </c>
       <c r="I20" s="1">
-        <v>1.58</v>
+        <v>62.26</v>
       </c>
       <c r="J20">
-        <v>83.76000000000001</v>
-      </c>
-      <c r="K20" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11">
+        <v>1.6</v>
+      </c>
+      <c r="K20" s="1">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="L20" t="s">
+        <v>104</v>
+      </c>
+      <c r="M20">
+        <v>48660</v>
+      </c>
+      <c r="N20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
       <c r="A21" s="3">
         <v>46192</v>
       </c>
       <c r="B21" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C21" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D21" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="E21" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F21">
-        <v>40.6</v>
-      </c>
-      <c r="G21" s="1">
+        <v>54</v>
+      </c>
+      <c r="G21" t="s">
+        <v>86</v>
+      </c>
+      <c r="H21">
         <v>1.53</v>
       </c>
-      <c r="H21">
-        <v>62.12</v>
-      </c>
       <c r="I21" s="1">
+        <v>82.62</v>
+      </c>
+      <c r="J21">
         <v>1.56</v>
       </c>
-      <c r="J21">
-        <v>63.34</v>
-      </c>
-      <c r="K21" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11">
+      <c r="K21" s="1">
+        <v>84.23999999999999</v>
+      </c>
+      <c r="L21" t="s">
+        <v>105</v>
+      </c>
+      <c r="M21">
+        <v>468368</v>
+      </c>
+      <c r="N21" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
       <c r="A22" s="3">
         <v>46192</v>
       </c>
       <c r="B22" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="C22" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D22" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="E22" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F22">
-        <v>41.73</v>
-      </c>
-      <c r="G22" s="1">
+        <v>40.6</v>
+      </c>
+      <c r="G22" t="s">
+        <v>86</v>
+      </c>
+      <c r="H22">
         <v>1.53</v>
       </c>
-      <c r="H22">
-        <v>63.85</v>
-      </c>
       <c r="I22" s="1">
+        <v>62.12</v>
+      </c>
+      <c r="J22">
         <v>1.56</v>
       </c>
-      <c r="J22">
-        <v>65.09999999999999</v>
-      </c>
-      <c r="K22" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11">
+      <c r="K22" s="1">
+        <v>63.34</v>
+      </c>
+      <c r="L22" t="s">
+        <v>106</v>
+      </c>
+      <c r="M22">
+        <v>173486</v>
+      </c>
+      <c r="N22" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
       <c r="A23" s="3">
         <v>46192</v>
       </c>
       <c r="B23" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C23" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D23" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E23" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F23">
-        <v>54</v>
-      </c>
-      <c r="G23" s="1">
+        <v>41.73</v>
+      </c>
+      <c r="G23" t="s">
+        <v>86</v>
+      </c>
+      <c r="H23">
         <v>1.53</v>
       </c>
-      <c r="H23">
-        <v>82.62</v>
-      </c>
       <c r="I23" s="1">
+        <v>63.85</v>
+      </c>
+      <c r="J23">
         <v>1.56</v>
       </c>
-      <c r="J23">
-        <v>84.23999999999999</v>
-      </c>
-      <c r="K23" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11">
+      <c r="K23" s="1">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="L23" t="s">
+        <v>107</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
       <c r="A24" s="3">
         <v>46195</v>
       </c>
       <c r="B24" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C24" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D24" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E24" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F24">
         <v>37.28</v>
       </c>
-      <c r="G24" s="1">
+      <c r="G24" t="s">
+        <v>86</v>
+      </c>
+      <c r="H24">
         <v>1.46</v>
       </c>
-      <c r="H24">
+      <c r="I24" s="1">
         <v>54.43</v>
       </c>
-      <c r="I24" s="1">
+      <c r="J24">
         <v>1.52</v>
       </c>
-      <c r="J24">
+      <c r="K24" s="1">
         <v>56.67</v>
       </c>
-      <c r="K24" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11">
+      <c r="L24" t="s">
+        <v>108</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
       <c r="A25" s="3">
         <v>46196</v>
       </c>
       <c r="B25" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C25" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D25" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E25" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F25">
         <v>45.76</v>
       </c>
-      <c r="G25" s="1">
+      <c r="G25" t="s">
+        <v>86</v>
+      </c>
+      <c r="H25">
         <v>1.46</v>
       </c>
-      <c r="H25">
+      <c r="I25" s="1">
         <v>66.81</v>
       </c>
-      <c r="I25" s="1">
+      <c r="J25">
         <v>1.52</v>
       </c>
-      <c r="J25">
+      <c r="K25" s="1">
         <v>69.56</v>
       </c>
-      <c r="K25" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11">
+      <c r="L25" t="s">
+        <v>109</v>
+      </c>
+      <c r="M25">
+        <v>226650</v>
+      </c>
+      <c r="N25" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
       <c r="A26" s="3">
         <v>46196</v>
       </c>
       <c r="B26" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C26" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D26" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E26" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F26">
-        <v>45.65</v>
-      </c>
-      <c r="G26" s="1">
+        <v>46.35</v>
+      </c>
+      <c r="G26" t="s">
+        <v>86</v>
+      </c>
+      <c r="H26">
         <v>1.46</v>
       </c>
-      <c r="H26">
-        <v>66.65000000000001</v>
-      </c>
       <c r="I26" s="1">
+        <v>67.67</v>
+      </c>
+      <c r="J26">
         <v>1.51</v>
       </c>
-      <c r="J26">
-        <v>68.93000000000001</v>
-      </c>
-      <c r="K26" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11">
+      <c r="K26" s="1">
+        <v>69.98999999999999</v>
+      </c>
+      <c r="L26" t="s">
+        <v>110</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
       <c r="A27" s="3">
         <v>46196</v>
       </c>
       <c r="B27" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C27" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="D27" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="E27" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F27">
-        <v>46.35</v>
-      </c>
-      <c r="G27" s="1">
+        <v>39.91</v>
+      </c>
+      <c r="G27" t="s">
+        <v>86</v>
+      </c>
+      <c r="H27">
         <v>1.46</v>
       </c>
-      <c r="H27">
-        <v>67.67</v>
-      </c>
       <c r="I27" s="1">
-        <v>1.51</v>
+        <v>58.27</v>
       </c>
       <c r="J27">
-        <v>69.98999999999999</v>
-      </c>
-      <c r="K27" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11">
+        <v>1.52</v>
+      </c>
+      <c r="K27" s="1">
+        <v>60.66</v>
+      </c>
+      <c r="L27" t="s">
+        <v>111</v>
+      </c>
+      <c r="M27">
+        <v>1448600</v>
+      </c>
+      <c r="N27" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
       <c r="A28" s="3">
         <v>46196</v>
       </c>
       <c r="B28" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="C28" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="D28" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="E28" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F28">
-        <v>39.91</v>
-      </c>
-      <c r="G28" s="1">
+        <v>34</v>
+      </c>
+      <c r="G28" t="s">
+        <v>86</v>
+      </c>
+      <c r="H28">
         <v>1.46</v>
       </c>
-      <c r="H28">
-        <v>58.27</v>
-      </c>
       <c r="I28" s="1">
+        <v>49.64</v>
+      </c>
+      <c r="J28">
         <v>1.52</v>
       </c>
-      <c r="J28">
-        <v>60.66</v>
-      </c>
-      <c r="K28" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11">
+      <c r="K28" s="1">
+        <v>51.68</v>
+      </c>
+      <c r="L28" t="s">
+        <v>112</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
       <c r="A29" s="3">
         <v>46196</v>
       </c>
       <c r="B29" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C29" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="D29" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="E29" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F29">
-        <v>34</v>
-      </c>
-      <c r="G29" s="1">
+        <v>45.65</v>
+      </c>
+      <c r="G29" t="s">
+        <v>86</v>
+      </c>
+      <c r="H29">
         <v>1.46</v>
       </c>
-      <c r="H29">
-        <v>49.64</v>
-      </c>
       <c r="I29" s="1">
-        <v>1.52</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="J29">
-        <v>51.68</v>
-      </c>
-      <c r="K29" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11">
+        <v>1.51</v>
+      </c>
+      <c r="K29" s="1">
+        <v>68.93000000000001</v>
+      </c>
+      <c r="L29" t="s">
+        <v>113</v>
+      </c>
+      <c r="M29">
+        <v>235361</v>
+      </c>
+      <c r="N29" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
       <c r="A30" s="3">
         <v>46197</v>
       </c>
       <c r="B30" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C30" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D30" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="E30" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F30">
-        <v>39.04</v>
-      </c>
-      <c r="G30" s="1">
+        <v>54.22</v>
+      </c>
+      <c r="G30" t="s">
+        <v>86</v>
+      </c>
+      <c r="H30">
         <v>1.45</v>
       </c>
-      <c r="H30">
-        <v>56.61</v>
-      </c>
       <c r="I30" s="1">
+        <v>78.62</v>
+      </c>
+      <c r="J30">
         <v>1.51</v>
       </c>
-      <c r="J30">
-        <v>58.95</v>
-      </c>
-      <c r="K30" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11">
+      <c r="K30" s="1">
+        <v>81.87</v>
+      </c>
+      <c r="L30" t="s">
+        <v>114</v>
+      </c>
+      <c r="M30">
+        <v>419467</v>
+      </c>
+      <c r="N30" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
       <c r="A31" s="3">
         <v>46197</v>
       </c>
       <c r="B31" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C31" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D31" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="E31" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F31">
-        <v>54.22</v>
-      </c>
-      <c r="G31" s="1">
+        <v>39.04</v>
+      </c>
+      <c r="G31" t="s">
+        <v>86</v>
+      </c>
+      <c r="H31">
         <v>1.45</v>
       </c>
-      <c r="H31">
-        <v>78.62</v>
-      </c>
       <c r="I31" s="1">
+        <v>56.61</v>
+      </c>
+      <c r="J31">
         <v>1.51</v>
       </c>
-      <c r="J31">
-        <v>81.87</v>
-      </c>
-      <c r="K31" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11">
+      <c r="K31" s="1">
+        <v>58.95</v>
+      </c>
+      <c r="L31" t="s">
+        <v>115</v>
+      </c>
+      <c r="M31">
+        <v>337934</v>
+      </c>
+      <c r="N31" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
       <c r="A32" s="3">
         <v>46198</v>
       </c>
       <c r="B32" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C32" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D32" t="s">
         <v>74</v>
       </c>
       <c r="E32" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F32">
-        <v>32.69</v>
-      </c>
-      <c r="G32" s="1">
+        <v>47</v>
+      </c>
+      <c r="G32" t="s">
+        <v>86</v>
+      </c>
+      <c r="H32">
         <v>1.45</v>
       </c>
-      <c r="H32">
-        <v>47.4</v>
-      </c>
       <c r="I32" s="1">
+        <v>68.15000000000001</v>
+      </c>
+      <c r="J32">
         <v>1.51</v>
       </c>
-      <c r="J32">
-        <v>49.36</v>
-      </c>
-      <c r="K32" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11">
+      <c r="K32" s="1">
+        <v>70.97</v>
+      </c>
+      <c r="L32" t="s">
+        <v>116</v>
+      </c>
+      <c r="M32">
+        <v>469232</v>
+      </c>
+      <c r="N32" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14">
       <c r="A33" s="3">
         <v>46198</v>
       </c>
       <c r="B33" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C33" t="s">
+        <v>57</v>
+      </c>
+      <c r="D33" t="s">
+        <v>79</v>
+      </c>
+      <c r="E33" t="s">
+        <v>81</v>
+      </c>
+      <c r="F33">
+        <v>32.69</v>
+      </c>
+      <c r="G33" t="s">
+        <v>86</v>
+      </c>
+      <c r="H33">
+        <v>1.45</v>
+      </c>
+      <c r="I33" s="1">
+        <v>47.4</v>
+      </c>
+      <c r="J33">
+        <v>1.51</v>
+      </c>
+      <c r="K33" s="1">
+        <v>49.36</v>
+      </c>
+      <c r="L33" t="s">
+        <v>117</v>
+      </c>
+      <c r="M33">
+        <v>175261</v>
+      </c>
+      <c r="N33" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14">
+      <c r="A34" s="3">
+        <v>46199</v>
+      </c>
+      <c r="B34" t="s">
+        <v>32</v>
+      </c>
+      <c r="C34" t="s">
+        <v>38</v>
+      </c>
+      <c r="D34" t="s">
+        <v>60</v>
+      </c>
+      <c r="E34" t="s">
+        <v>81</v>
+      </c>
+      <c r="F34">
+        <v>24</v>
+      </c>
+      <c r="G34" t="s">
+        <v>86</v>
+      </c>
+      <c r="H34">
+        <v>1.43</v>
+      </c>
+      <c r="I34" s="1">
+        <v>34.32</v>
+      </c>
+      <c r="J34">
+        <v>1.5</v>
+      </c>
+      <c r="K34" s="1">
+        <v>36</v>
+      </c>
+      <c r="L34" t="s">
+        <v>118</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="N34" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14">
+      <c r="A35" s="3">
+        <v>46199</v>
+      </c>
+      <c r="B35" t="s">
+        <v>22</v>
+      </c>
+      <c r="C35" t="s">
+        <v>46</v>
+      </c>
+      <c r="D35" t="s">
+        <v>68</v>
+      </c>
+      <c r="E35" t="s">
+        <v>81</v>
+      </c>
+      <c r="F35">
+        <v>50</v>
+      </c>
+      <c r="G35" t="s">
+        <v>86</v>
+      </c>
+      <c r="H35">
+        <v>1.43</v>
+      </c>
+      <c r="I35" s="1">
+        <v>71.5</v>
+      </c>
+      <c r="J35">
+        <v>1.51</v>
+      </c>
+      <c r="K35" s="1">
+        <v>75.5</v>
+      </c>
+      <c r="L35" t="s">
+        <v>119</v>
+      </c>
+      <c r="M35">
+        <v>574444</v>
+      </c>
+      <c r="N35" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14">
+      <c r="A36" s="3">
+        <v>46199</v>
+      </c>
+      <c r="B36" t="s">
+        <v>34</v>
+      </c>
+      <c r="C36" t="s">
+        <v>58</v>
+      </c>
+      <c r="D36" t="s">
+        <v>80</v>
+      </c>
+      <c r="E36" t="s">
+        <v>81</v>
+      </c>
+      <c r="F36">
+        <v>43.28</v>
+      </c>
+      <c r="G36" t="s">
+        <v>86</v>
+      </c>
+      <c r="H36">
+        <v>1.43</v>
+      </c>
+      <c r="I36" s="1">
+        <v>61.89</v>
+      </c>
+      <c r="J36">
+        <v>1.5</v>
+      </c>
+      <c r="K36" s="1">
+        <v>64.92</v>
+      </c>
+      <c r="L36" t="s">
+        <v>120</v>
+      </c>
+      <c r="M36">
+        <v>162923</v>
+      </c>
+      <c r="N36" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14">
+      <c r="A37" s="3">
+        <v>46202</v>
+      </c>
+      <c r="B37" t="s">
+        <v>30</v>
+      </c>
+      <c r="C37" t="s">
+        <v>52</v>
+      </c>
+      <c r="D37" t="s">
+        <v>74</v>
+      </c>
+      <c r="E37" t="s">
+        <v>81</v>
+      </c>
+      <c r="F37">
+        <v>27</v>
+      </c>
+      <c r="G37" t="s">
+        <v>86</v>
+      </c>
+      <c r="H37">
+        <v>1.42</v>
+      </c>
+      <c r="I37" s="1">
+        <v>38.34</v>
+      </c>
+      <c r="J37">
+        <v>1.51</v>
+      </c>
+      <c r="K37" s="1">
+        <v>40.77</v>
+      </c>
+      <c r="L37" t="s">
+        <v>121</v>
+      </c>
+      <c r="M37">
+        <v>469688</v>
+      </c>
+      <c r="N37" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14">
+      <c r="A38" s="3">
+        <v>46202</v>
+      </c>
+      <c r="B38" t="s">
+        <v>25</v>
+      </c>
+      <c r="C38" t="s">
+        <v>45</v>
+      </c>
+      <c r="D38" t="s">
+        <v>67</v>
+      </c>
+      <c r="E38" t="s">
+        <v>81</v>
+      </c>
+      <c r="F38">
+        <v>40.13</v>
+      </c>
+      <c r="G38" t="s">
+        <v>86</v>
+      </c>
+      <c r="H38">
+        <v>1.42</v>
+      </c>
+      <c r="I38" s="1">
+        <v>56.98</v>
+      </c>
+      <c r="J38">
+        <v>1.51</v>
+      </c>
+      <c r="K38" s="1">
+        <v>60.6</v>
+      </c>
+      <c r="L38" t="s">
+        <v>122</v>
+      </c>
+      <c r="M38">
+        <v>236173</v>
+      </c>
+      <c r="N38" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14">
+      <c r="A39" s="3">
+        <v>46202</v>
+      </c>
+      <c r="B39" t="s">
+        <v>25</v>
+      </c>
+      <c r="C39" t="s">
+        <v>48</v>
+      </c>
+      <c r="D39" t="s">
+        <v>70</v>
+      </c>
+      <c r="E39" t="s">
+        <v>84</v>
+      </c>
+      <c r="F39">
+        <v>43.35</v>
+      </c>
+      <c r="G39" t="s">
+        <v>86</v>
+      </c>
+      <c r="H39">
+        <v>1.38</v>
+      </c>
+      <c r="I39" s="1">
+        <v>59.82</v>
+      </c>
+      <c r="J39">
+        <v>1.5</v>
+      </c>
+      <c r="K39" s="1">
+        <v>65.03</v>
+      </c>
+      <c r="L39" t="s">
+        <v>123</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="N39" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14">
+      <c r="A40" s="3">
+        <v>46202</v>
+      </c>
+      <c r="B40" t="s">
+        <v>25</v>
+      </c>
+      <c r="C40" t="s">
+        <v>54</v>
+      </c>
+      <c r="D40" t="s">
+        <v>76</v>
+      </c>
+      <c r="E40" t="s">
+        <v>81</v>
+      </c>
+      <c r="F40">
+        <v>51.26</v>
+      </c>
+      <c r="G40" t="s">
+        <v>86</v>
+      </c>
+      <c r="H40">
+        <v>1.42</v>
+      </c>
+      <c r="I40" s="1">
+        <v>72.79000000000001</v>
+      </c>
+      <c r="J40">
+        <v>1.51</v>
+      </c>
+      <c r="K40" s="1">
+        <v>77.40000000000001</v>
+      </c>
+      <c r="L40" t="s">
+        <v>124</v>
+      </c>
+      <c r="M40">
+        <v>145662</v>
+      </c>
+      <c r="N40" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14">
+      <c r="A41" s="3">
+        <v>46203</v>
+      </c>
+      <c r="B41" t="s">
+        <v>16</v>
+      </c>
+      <c r="C41" t="s">
+        <v>39</v>
+      </c>
+      <c r="D41" t="s">
+        <v>61</v>
+      </c>
+      <c r="E41" t="s">
+        <v>81</v>
+      </c>
+      <c r="F41">
+        <v>28.66</v>
+      </c>
+      <c r="G41" t="s">
+        <v>86</v>
+      </c>
+      <c r="H41">
+        <v>1.42</v>
+      </c>
+      <c r="I41" s="1">
+        <v>40.7</v>
+      </c>
+      <c r="J41">
+        <v>1.52</v>
+      </c>
+      <c r="K41" s="1">
+        <v>43.56</v>
+      </c>
+      <c r="L41" t="s">
+        <v>125</v>
+      </c>
+      <c r="M41">
+        <v>0</v>
+      </c>
+      <c r="N41" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14">
+      <c r="A42" s="3">
+        <v>46203</v>
+      </c>
+      <c r="B42" t="s">
+        <v>25</v>
+      </c>
+      <c r="C42" t="s">
+        <v>41</v>
+      </c>
+      <c r="D42" t="s">
+        <v>63</v>
+      </c>
+      <c r="E42" t="s">
+        <v>81</v>
+      </c>
+      <c r="F42">
+        <v>80.61</v>
+      </c>
+      <c r="G42" t="s">
+        <v>86</v>
+      </c>
+      <c r="H42">
+        <v>1.42</v>
+      </c>
+      <c r="I42" s="1">
+        <v>114.47</v>
+      </c>
+      <c r="J42">
+        <v>1.51</v>
+      </c>
+      <c r="K42" s="1">
+        <v>121.72</v>
+      </c>
+      <c r="L42" t="s">
+        <v>126</v>
+      </c>
+      <c r="M42">
+        <v>0</v>
+      </c>
+      <c r="N42" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14">
+      <c r="A43" s="3">
+        <v>46203</v>
+      </c>
+      <c r="B43" t="s">
+        <v>25</v>
+      </c>
+      <c r="C43" t="s">
+        <v>45</v>
+      </c>
+      <c r="D43" t="s">
+        <v>67</v>
+      </c>
+      <c r="E43" t="s">
+        <v>81</v>
+      </c>
+      <c r="F43">
+        <v>12.16</v>
+      </c>
+      <c r="G43" t="s">
+        <v>86</v>
+      </c>
+      <c r="H43">
+        <v>1.42</v>
+      </c>
+      <c r="I43" s="1">
+        <v>17.27</v>
+      </c>
+      <c r="J43">
+        <v>1.51</v>
+      </c>
+      <c r="K43" s="1">
+        <v>18.36</v>
+      </c>
+      <c r="L43" t="s">
+        <v>127</v>
+      </c>
+      <c r="M43">
+        <v>236385</v>
+      </c>
+      <c r="N43" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14">
+      <c r="A44" s="3">
+        <v>46203</v>
+      </c>
+      <c r="B44" t="s">
+        <v>26</v>
+      </c>
+      <c r="C44" t="s">
         <v>49</v>
       </c>
-      <c r="D33" t="s">
-        <v>70</v>
-      </c>
-      <c r="E33" t="s">
+      <c r="D44" t="s">
+        <v>71</v>
+      </c>
+      <c r="E44" t="s">
+        <v>81</v>
+      </c>
+      <c r="F44">
+        <v>57</v>
+      </c>
+      <c r="G44" t="s">
+        <v>86</v>
+      </c>
+      <c r="H44">
+        <v>1.42</v>
+      </c>
+      <c r="I44" s="1">
+        <v>80.94</v>
+      </c>
+      <c r="J44">
+        <v>1.51</v>
+      </c>
+      <c r="K44" s="1">
+        <v>86.06999999999999</v>
+      </c>
+      <c r="L44" t="s">
+        <v>128</v>
+      </c>
+      <c r="M44">
+        <v>389354</v>
+      </c>
+      <c r="N44" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14">
+      <c r="A45" s="3">
+        <v>46203</v>
+      </c>
+      <c r="B45" t="s">
+        <v>22</v>
+      </c>
+      <c r="C45" t="s">
+        <v>46</v>
+      </c>
+      <c r="D45" t="s">
+        <v>68</v>
+      </c>
+      <c r="E45" t="s">
+        <v>81</v>
+      </c>
+      <c r="F45">
+        <v>12.98</v>
+      </c>
+      <c r="G45" t="s">
+        <v>86</v>
+      </c>
+      <c r="H45">
+        <v>1.42</v>
+      </c>
+      <c r="I45" s="1">
+        <v>18.43</v>
+      </c>
+      <c r="J45">
+        <v>1.51</v>
+      </c>
+      <c r="K45" s="1">
+        <v>19.6</v>
+      </c>
+      <c r="L45" t="s">
+        <v>129</v>
+      </c>
+      <c r="M45">
+        <v>574635</v>
+      </c>
+      <c r="N45" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14">
+      <c r="A46" s="3">
+        <v>46203</v>
+      </c>
+      <c r="B46" t="s">
+        <v>27</v>
+      </c>
+      <c r="C46" t="s">
+        <v>53</v>
+      </c>
+      <c r="D46" t="s">
         <v>75</v>
       </c>
-      <c r="F33">
-        <v>47</v>
-      </c>
-      <c r="G33" s="1">
-        <v>1.45</v>
-      </c>
-      <c r="H33">
-        <v>68.15000000000001</v>
-      </c>
-      <c r="I33" s="1">
+      <c r="E46" t="s">
+        <v>81</v>
+      </c>
+      <c r="F46">
+        <v>23.97</v>
+      </c>
+      <c r="G46" t="s">
+        <v>86</v>
+      </c>
+      <c r="H46">
+        <v>1.42</v>
+      </c>
+      <c r="I46" s="1">
+        <v>34.04</v>
+      </c>
+      <c r="J46">
         <v>1.51</v>
       </c>
-      <c r="J33">
-        <v>70.97</v>
-      </c>
-      <c r="K33" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11">
-      <c r="A36" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
-    </row>
-    <row r="37" spans="1:11">
-      <c r="A37" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="E37" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F37" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11">
-      <c r="A38" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="B38" s="7">
-        <v>1227.87</v>
-      </c>
-      <c r="C38" s="7">
-        <v>28</v>
-      </c>
-      <c r="D38" s="8">
-        <v>1.5073</v>
-      </c>
-      <c r="E38" s="7">
-        <v>1850.8</v>
-      </c>
-      <c r="F38" s="7">
-        <v>1915.87</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11">
-      <c r="A39" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="B39" s="7">
-        <v>68.09</v>
-      </c>
-      <c r="C39" s="7">
-        <v>2</v>
-      </c>
-      <c r="D39" s="8">
-        <v>1.45</v>
-      </c>
-      <c r="E39" s="7">
-        <v>98.73</v>
-      </c>
-      <c r="F39" s="7">
-        <v>105.54</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11">
-      <c r="A40" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="B40" s="7">
+      <c r="K46" s="1">
+        <v>36.19</v>
+      </c>
+      <c r="L46" t="s">
+        <v>130</v>
+      </c>
+      <c r="M46">
+        <v>173945</v>
+      </c>
+      <c r="N46" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14">
+      <c r="A47" s="3">
+        <v>46203</v>
+      </c>
+      <c r="B47" t="s">
+        <v>19</v>
+      </c>
+      <c r="C47" t="s">
+        <v>42</v>
+      </c>
+      <c r="D47" t="s">
+        <v>64</v>
+      </c>
+      <c r="E47" t="s">
+        <v>81</v>
+      </c>
+      <c r="F47">
+        <v>45.31</v>
+      </c>
+      <c r="G47" t="s">
+        <v>86</v>
+      </c>
+      <c r="H47">
+        <v>1.42</v>
+      </c>
+      <c r="I47" s="1">
+        <v>64.34</v>
+      </c>
+      <c r="J47">
+        <v>1.51</v>
+      </c>
+      <c r="K47" s="1">
+        <v>68.42</v>
+      </c>
+      <c r="L47" t="s">
+        <v>131</v>
+      </c>
+      <c r="M47">
+        <v>0</v>
+      </c>
+      <c r="N47" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14">
+      <c r="A48" s="3">
+        <v>46203</v>
+      </c>
+      <c r="B48" t="s">
+        <v>20</v>
+      </c>
+      <c r="C48" t="s">
+        <v>43</v>
+      </c>
+      <c r="D48" t="s">
+        <v>65</v>
+      </c>
+      <c r="E48" t="s">
+        <v>81</v>
+      </c>
+      <c r="F48">
+        <v>38</v>
+      </c>
+      <c r="G48" t="s">
+        <v>86</v>
+      </c>
+      <c r="H48">
+        <v>1.42</v>
+      </c>
+      <c r="I48" s="1">
+        <v>53.96</v>
+      </c>
+      <c r="J48">
+        <v>1.51</v>
+      </c>
+      <c r="K48" s="1">
+        <v>57.38</v>
+      </c>
+      <c r="L48" t="s">
+        <v>132</v>
+      </c>
+      <c r="M48">
+        <v>416015</v>
+      </c>
+      <c r="N48" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14">
+      <c r="A49" s="3">
+        <v>46203</v>
+      </c>
+      <c r="B49" t="s">
+        <v>36</v>
+      </c>
+      <c r="C49" t="s">
+        <v>50</v>
+      </c>
+      <c r="D49" t="s">
+        <v>72</v>
+      </c>
+      <c r="E49" t="s">
+        <v>85</v>
+      </c>
+      <c r="F49">
+        <v>51.95</v>
+      </c>
+      <c r="G49" t="s">
+        <v>86</v>
+      </c>
+      <c r="H49">
+        <v>1.79</v>
+      </c>
+      <c r="I49" s="1">
+        <v>92.98999999999999</v>
+      </c>
+      <c r="J49">
+        <v>1.79</v>
+      </c>
+      <c r="K49" s="1">
+        <v>92.98999999999999</v>
+      </c>
+      <c r="L49" t="s">
+        <v>133</v>
+      </c>
+      <c r="M49">
+        <v>0</v>
+      </c>
+      <c r="N49" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14">
+      <c r="A52" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B52" s="4"/>
+      <c r="C52" s="4"/>
+      <c r="D52" s="4"/>
+      <c r="E52" s="4"/>
+      <c r="F52" s="4"/>
+    </row>
+    <row r="53" spans="1:14">
+      <c r="A53" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="E53" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F53" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14">
+      <c r="A54" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B54" s="7">
+        <v>1762.23</v>
+      </c>
+      <c r="C54" s="7">
+        <v>42</v>
+      </c>
+      <c r="D54" s="8">
+        <v>1.4815</v>
+      </c>
+      <c r="E54" s="7">
+        <v>2610.77</v>
+      </c>
+      <c r="F54" s="7">
+        <v>2722.36</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14">
+      <c r="A55" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="B55" s="7">
+        <v>111.44</v>
+      </c>
+      <c r="C55" s="7">
+        <v>3</v>
+      </c>
+      <c r="D55" s="8">
+        <v>1.4227</v>
+      </c>
+      <c r="E55" s="7">
+        <v>158.55</v>
+      </c>
+      <c r="F55" s="7">
+        <v>170.57</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14">
+      <c r="A56" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="B56" s="7">
+        <v>51.95</v>
+      </c>
+      <c r="C56" s="7">
+        <v>1</v>
+      </c>
+      <c r="D56" s="8">
+        <v>1.79</v>
+      </c>
+      <c r="E56" s="7">
+        <v>92.98999999999999</v>
+      </c>
+      <c r="F56" s="7">
+        <v>92.98999999999999</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14">
+      <c r="A57" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B57" s="7">
         <v>15.52</v>
       </c>
-      <c r="C40" s="7">
+      <c r="C57" s="7">
         <v>1</v>
       </c>
-      <c r="D40" s="8">
+      <c r="D57" s="8">
         <v>1.1701</v>
       </c>
-      <c r="E40" s="7">
+      <c r="E57" s="7">
         <v>18.16</v>
       </c>
-      <c r="F40" s="7">
+      <c r="F57" s="7">
         <v>18.16</v>
       </c>
     </row>
-    <row r="41" spans="1:11">
-      <c r="A41" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="B41" s="7">
+    <row r="58" spans="1:14">
+      <c r="A58" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B58" s="7">
         <v>1</v>
       </c>
-      <c r="C41" s="7">
+      <c r="C58" s="7">
         <v>1</v>
       </c>
-      <c r="D41" s="8">
+      <c r="D58" s="8">
         <v>3.52</v>
       </c>
-      <c r="E41" s="7">
+      <c r="E58" s="7">
         <v>3.52</v>
       </c>
-      <c r="F41" s="7">
+      <c r="F58" s="7">
         <v>3.52</v>
       </c>
     </row>
-    <row r="42" spans="1:11">
-      <c r="A42" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="B42" s="10">
-        <v>1312.48</v>
-      </c>
-      <c r="C42" s="10">
-        <v>32</v>
-      </c>
-      <c r="D42" s="8"/>
-      <c r="E42" s="10">
-        <v>1971.21</v>
-      </c>
-      <c r="F42" s="10">
-        <v>2043.09</v>
+    <row r="59" spans="1:14">
+      <c r="A59" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="B59" s="10">
+        <v>1942.14</v>
+      </c>
+      <c r="C59" s="10">
+        <v>48</v>
+      </c>
+      <c r="D59" s="8"/>
+      <c r="E59" s="10">
+        <v>2883.99</v>
+      </c>
+      <c r="F59" s="10">
+        <v>3007.6</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="A52:F52"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/МЕРКУРИЙ ПРОИЗВОДСТВО И ПАКЕТАЖ АД/МЕРКУРИЙ ПРОИЗВОДСТВО И ПАКЕТАЖ АД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/МЕРКУРИЙ ПРОИЗВОДСТВО И ПАКЕТАЖ АД/МЕРКУРИЙ ПРОИЗВОДСТВО И ПАКЕТАЖ АД.xlsx
@@ -596,7 +596,7 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -3468,7 +3468,7 @@
         <v>46</v>
       </c>
       <c r="D60" s="8">
-        <v>1.6333</v>
+        <v>1.633279</v>
       </c>
       <c r="E60" s="7">
         <v>3257.02</v>
@@ -3508,7 +3508,7 @@
         <v>1</v>
       </c>
       <c r="D62" s="8">
-        <v>2.0201</v>
+        <v>2.020088</v>
       </c>
       <c r="E62" s="7">
         <v>82.45999999999999</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/МЕРКУРИЙ ПРОИЗВОДСТВО И ПАКЕТАЖ АД/МЕРКУРИЙ ПРОИЗВОДСТВО И ПАКЕТАЖ АД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/МЕРКУРИЙ ПРОИЗВОДСТВО И ПАКЕТАЖ АД/МЕРКУРИЙ ПРОИЗВОДСТВО И ПАКЕТАЖ АД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="192">
   <si>
     <t>Дата</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>Тип количество</t>
+  </si>
+  <si>
+    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -988,7 +991,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N68"/>
+  <dimension ref="A1:O68"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -1001,13 +1004,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1050,688 +1053,736 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" s="3">
         <v>46219</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F2">
-        <v>44.66</v>
+        <v>44.663</v>
       </c>
       <c r="G2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H2">
-        <v>1.52</v>
+        <v>1.499</v>
       </c>
       <c r="I2" s="1">
-        <v>67.88</v>
+        <v>1.519</v>
       </c>
       <c r="J2">
+        <v>67.843097</v>
+      </c>
+      <c r="K2" s="1">
         <v>1.6</v>
       </c>
-      <c r="K2" s="1">
-        <v>71.45999999999999</v>
-      </c>
-      <c r="L2" t="s">
-        <v>90</v>
-      </c>
-      <c r="M2">
+      <c r="L2" s="1">
+        <v>71.46080000000001</v>
+      </c>
+      <c r="M2" t="s">
+        <v>91</v>
+      </c>
+      <c r="N2">
         <v>420393</v>
       </c>
-      <c r="N2" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+      <c r="O2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" s="3">
         <v>46219</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F3">
-        <v>43.79</v>
+        <v>43.789</v>
       </c>
       <c r="G3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H3">
-        <v>1.52</v>
+        <v>1.499</v>
       </c>
       <c r="I3" s="1">
-        <v>66.56</v>
+        <v>1.519</v>
       </c>
       <c r="J3">
+        <v>66.515491</v>
+      </c>
+      <c r="K3" s="1">
         <v>1.61</v>
       </c>
-      <c r="K3" s="1">
-        <v>70.5</v>
-      </c>
-      <c r="L3" t="s">
-        <v>91</v>
-      </c>
-      <c r="M3">
+      <c r="L3" s="1">
+        <v>70.50029000000001</v>
+      </c>
+      <c r="M3" t="s">
+        <v>92</v>
+      </c>
+      <c r="N3">
         <v>0</v>
       </c>
-      <c r="N3" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+      <c r="O3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" s="3">
         <v>46219</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F4">
         <v>41.84</v>
       </c>
       <c r="G4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H4">
-        <v>1.52</v>
+        <v>1.499</v>
       </c>
       <c r="I4" s="1">
-        <v>63.6</v>
+        <v>1.519</v>
       </c>
       <c r="J4">
+        <v>63.55496</v>
+      </c>
+      <c r="K4" s="1">
         <v>1.62</v>
       </c>
-      <c r="K4" s="1">
-        <v>67.78</v>
-      </c>
-      <c r="L4" t="s">
-        <v>92</v>
-      </c>
-      <c r="M4">
+      <c r="L4" s="1">
+        <v>67.7808</v>
+      </c>
+      <c r="M4" t="s">
+        <v>93</v>
+      </c>
+      <c r="N4">
         <v>238082</v>
       </c>
-      <c r="N4" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+      <c r="O4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5" s="3">
         <v>46220</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F5">
         <v>43</v>
       </c>
       <c r="G5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H5">
-        <v>1.52</v>
+        <v>1.499</v>
       </c>
       <c r="I5" s="1">
-        <v>65.36</v>
+        <v>1.519</v>
       </c>
       <c r="J5">
+        <v>65.31699999999999</v>
+      </c>
+      <c r="K5" s="1">
         <v>1.62</v>
       </c>
-      <c r="K5" s="1">
+      <c r="L5" s="1">
         <v>69.66</v>
       </c>
-      <c r="L5" t="s">
-        <v>93</v>
-      </c>
-      <c r="M5">
+      <c r="M5" t="s">
+        <v>94</v>
+      </c>
+      <c r="N5">
         <v>470400</v>
       </c>
-      <c r="N5" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+      <c r="O5" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6" s="3">
         <v>46220</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F6">
-        <v>45.21</v>
+        <v>45.209</v>
       </c>
       <c r="G6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H6">
-        <v>1.52</v>
+        <v>1.499</v>
       </c>
       <c r="I6" s="1">
-        <v>68.72</v>
+        <v>1.519</v>
       </c>
       <c r="J6">
+        <v>68.672471</v>
+      </c>
+      <c r="K6" s="1">
         <v>1.63</v>
       </c>
-      <c r="K6" s="1">
-        <v>73.69</v>
-      </c>
-      <c r="L6" t="s">
-        <v>94</v>
-      </c>
-      <c r="M6">
+      <c r="L6" s="1">
+        <v>73.69067</v>
+      </c>
+      <c r="M6" t="s">
+        <v>95</v>
+      </c>
+      <c r="N6">
         <v>175575</v>
       </c>
-      <c r="N6" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+      <c r="O6" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7" s="3">
         <v>46223</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F7">
         <v>43</v>
       </c>
       <c r="G7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H7">
-        <v>1.57</v>
+        <v>1.546</v>
       </c>
       <c r="I7" s="1">
-        <v>67.51000000000001</v>
+        <v>1.566</v>
       </c>
       <c r="J7">
+        <v>67.33799999999999</v>
+      </c>
+      <c r="K7" s="1">
         <v>1.67</v>
       </c>
-      <c r="K7" s="1">
+      <c r="L7" s="1">
         <v>71.81</v>
       </c>
-      <c r="L7" t="s">
-        <v>95</v>
-      </c>
-      <c r="M7">
+      <c r="M7" t="s">
+        <v>96</v>
+      </c>
+      <c r="N7">
         <v>0</v>
       </c>
-      <c r="N7" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+      <c r="O7" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8" s="3">
         <v>46223</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F8">
         <v>43.03</v>
       </c>
       <c r="G8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H8">
-        <v>1.57</v>
+        <v>1.546</v>
       </c>
       <c r="I8" s="1">
-        <v>67.56</v>
+        <v>1.566</v>
       </c>
       <c r="J8">
+        <v>67.38498</v>
+      </c>
+      <c r="K8" s="1">
         <v>1.68</v>
       </c>
-      <c r="K8" s="1">
-        <v>72.29000000000001</v>
-      </c>
-      <c r="L8" t="s">
-        <v>96</v>
-      </c>
-      <c r="M8">
+      <c r="L8" s="1">
+        <v>72.29040000000001</v>
+      </c>
+      <c r="M8" t="s">
+        <v>97</v>
+      </c>
+      <c r="N8">
         <v>0</v>
       </c>
-      <c r="N8" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
+      <c r="O8" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
       <c r="A9" s="3">
         <v>46223</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F9">
         <v>55</v>
       </c>
       <c r="G9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H9">
-        <v>1.57</v>
+        <v>1.546</v>
       </c>
       <c r="I9" s="1">
-        <v>86.34999999999999</v>
+        <v>1.566</v>
       </c>
       <c r="J9">
+        <v>86.13</v>
+      </c>
+      <c r="K9" s="1">
         <v>1.68</v>
       </c>
-      <c r="K9" s="1">
+      <c r="L9" s="1">
         <v>92.40000000000001</v>
       </c>
-      <c r="L9" t="s">
-        <v>97</v>
-      </c>
-      <c r="M9">
+      <c r="M9" t="s">
+        <v>98</v>
+      </c>
+      <c r="N9">
         <v>576340</v>
       </c>
-      <c r="N9" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+      <c r="O9" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
       <c r="A10" s="3">
         <v>46224</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F10">
         <v>37</v>
       </c>
       <c r="G10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H10">
-        <v>1.58</v>
+        <v>1.564</v>
       </c>
       <c r="I10" s="1">
-        <v>58.46</v>
+        <v>1.584</v>
       </c>
       <c r="J10">
+        <v>58.608</v>
+      </c>
+      <c r="K10" s="1">
         <v>1.68</v>
       </c>
-      <c r="K10" s="1">
+      <c r="L10" s="1">
         <v>62.16</v>
       </c>
-      <c r="L10" t="s">
-        <v>98</v>
-      </c>
-      <c r="M10">
+      <c r="M10" t="s">
+        <v>99</v>
+      </c>
+      <c r="N10">
         <v>0</v>
       </c>
-      <c r="N10" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
+      <c r="O10" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
       <c r="A11" s="3">
         <v>46224</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F11">
-        <v>62.2</v>
+        <v>62.202</v>
       </c>
       <c r="G11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H11">
-        <v>1.58</v>
+        <v>1.564</v>
       </c>
       <c r="I11" s="1">
-        <v>98.28</v>
+        <v>1.584</v>
       </c>
       <c r="J11">
+        <v>98.527968</v>
+      </c>
+      <c r="K11" s="1">
         <v>1.68</v>
       </c>
-      <c r="K11" s="1">
-        <v>104.5</v>
-      </c>
-      <c r="L11" t="s">
-        <v>99</v>
-      </c>
-      <c r="M11">
+      <c r="L11" s="1">
+        <v>104.49936</v>
+      </c>
+      <c r="M11" t="s">
+        <v>100</v>
+      </c>
+      <c r="N11">
         <v>0</v>
       </c>
-      <c r="N11" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
+      <c r="O11" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
       <c r="A12" s="3">
         <v>46224</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E12" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F12">
-        <v>78.79000000000001</v>
+        <v>78.792</v>
       </c>
       <c r="G12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H12">
-        <v>1.58</v>
+        <v>1.564</v>
       </c>
       <c r="I12" s="1">
-        <v>124.49</v>
+        <v>1.584</v>
       </c>
       <c r="J12">
+        <v>124.806528</v>
+      </c>
+      <c r="K12" s="1">
         <v>1.68</v>
       </c>
-      <c r="K12" s="1">
-        <v>132.37</v>
-      </c>
-      <c r="L12" t="s">
-        <v>100</v>
-      </c>
-      <c r="M12">
+      <c r="L12" s="1">
+        <v>132.37056</v>
+      </c>
+      <c r="M12" t="s">
+        <v>101</v>
+      </c>
+      <c r="N12">
         <v>0</v>
       </c>
-      <c r="N12" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
+      <c r="O12" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
       <c r="A13" s="3">
         <v>46225</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D13" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E13" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F13">
         <v>40</v>
       </c>
       <c r="G13" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H13">
-        <v>1.61</v>
+        <v>1.588</v>
       </c>
       <c r="I13" s="1">
-        <v>64.40000000000001</v>
+        <v>1.608</v>
       </c>
       <c r="J13">
+        <v>64.31999999999999</v>
+      </c>
+      <c r="K13" s="1">
         <v>1.69</v>
       </c>
-      <c r="K13" s="1">
+      <c r="L13" s="1">
         <v>67.59999999999999</v>
       </c>
-      <c r="L13" t="s">
-        <v>101</v>
-      </c>
-      <c r="M13">
+      <c r="M13" t="s">
+        <v>102</v>
+      </c>
+      <c r="N13">
         <v>228700</v>
       </c>
-      <c r="N13" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
+      <c r="O13" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
       <c r="A14" s="3">
         <v>46225</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E14" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F14">
-        <v>50.34</v>
+        <v>50.343</v>
       </c>
       <c r="G14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H14">
-        <v>1.61</v>
+        <v>1.588</v>
       </c>
       <c r="I14" s="1">
-        <v>81.05</v>
+        <v>1.608</v>
       </c>
       <c r="J14">
+        <v>80.951544</v>
+      </c>
+      <c r="K14" s="1">
         <v>1.69</v>
       </c>
-      <c r="K14" s="1">
-        <v>85.06999999999999</v>
-      </c>
-      <c r="L14" t="s">
-        <v>102</v>
-      </c>
-      <c r="M14">
+      <c r="L14" s="1">
+        <v>85.07966999999999</v>
+      </c>
+      <c r="M14" t="s">
+        <v>103</v>
+      </c>
+      <c r="N14">
         <v>421251</v>
       </c>
-      <c r="N14" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
+      <c r="O14" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
       <c r="A15" s="3">
         <v>46225</v>
       </c>
       <c r="B15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C15" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D15" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E15" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F15">
-        <v>53.09</v>
+        <v>53.089</v>
       </c>
       <c r="G15" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H15">
-        <v>1.61</v>
+        <v>1.588</v>
       </c>
       <c r="I15" s="1">
-        <v>85.47</v>
+        <v>1.608</v>
       </c>
       <c r="J15">
+        <v>85.36711200000001</v>
+      </c>
+      <c r="K15" s="1">
         <v>1.69</v>
       </c>
-      <c r="K15" s="1">
-        <v>89.72</v>
-      </c>
-      <c r="L15" t="s">
-        <v>103</v>
-      </c>
-      <c r="M15">
+      <c r="L15" s="1">
+        <v>89.72041</v>
+      </c>
+      <c r="M15" t="s">
+        <v>104</v>
+      </c>
+      <c r="N15">
         <v>420909</v>
       </c>
-      <c r="N15" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
+      <c r="O15" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
       <c r="A16" s="3">
         <v>46225</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C16" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D16" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E16" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F16">
         <v>59.2</v>
       </c>
       <c r="G16" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H16">
-        <v>1.61</v>
+        <v>1.588</v>
       </c>
       <c r="I16" s="1">
-        <v>95.31</v>
+        <v>1.608</v>
       </c>
       <c r="J16">
+        <v>95.1936</v>
+      </c>
+      <c r="K16" s="1">
         <v>1.7</v>
       </c>
-      <c r="K16" s="1">
+      <c r="L16" s="1">
         <v>100.64</v>
       </c>
-      <c r="L16" t="s">
-        <v>104</v>
-      </c>
-      <c r="M16">
+      <c r="M16" t="s">
+        <v>105</v>
+      </c>
+      <c r="N16">
         <v>0</v>
       </c>
-      <c r="N16" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14">
+      <c r="O16" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15">
       <c r="A17" s="3">
         <v>46225</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C17" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E17" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F17">
         <v>1</v>
       </c>
       <c r="G17" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H17">
         <v>1.02</v>
@@ -1745,125 +1796,134 @@
       <c r="K17" s="1">
         <v>1.02</v>
       </c>
-      <c r="L17" t="s">
-        <v>104</v>
-      </c>
-      <c r="M17">
+      <c r="L17" s="1">
+        <v>1.02</v>
+      </c>
+      <c r="M17" t="s">
+        <v>105</v>
+      </c>
+      <c r="N17">
         <v>0</v>
       </c>
-      <c r="N17" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14">
+      <c r="O17" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15">
       <c r="A18" s="3">
         <v>46225</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D18" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E18" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F18">
-        <v>50.22</v>
+        <v>50.218</v>
       </c>
       <c r="G18" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H18">
-        <v>1.61</v>
+        <v>1.588</v>
       </c>
       <c r="I18" s="1">
-        <v>80.84999999999999</v>
+        <v>1.608</v>
       </c>
       <c r="J18">
+        <v>80.750544</v>
+      </c>
+      <c r="K18" s="1">
         <v>1.7</v>
       </c>
-      <c r="K18" s="1">
-        <v>85.37</v>
-      </c>
-      <c r="L18" t="s">
-        <v>105</v>
-      </c>
-      <c r="M18">
+      <c r="L18" s="1">
+        <v>85.3706</v>
+      </c>
+      <c r="M18" t="s">
+        <v>106</v>
+      </c>
+      <c r="N18">
         <v>0</v>
       </c>
-      <c r="N18" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14">
+      <c r="O18" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15">
       <c r="A19" s="3">
         <v>46226</v>
       </c>
       <c r="B19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C19" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D19" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E19" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F19">
         <v>44.7</v>
       </c>
       <c r="G19" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H19">
-        <v>1.61</v>
+        <v>1.588</v>
       </c>
       <c r="I19" s="1">
-        <v>71.97</v>
+        <v>1.608</v>
       </c>
       <c r="J19">
+        <v>71.8776</v>
+      </c>
+      <c r="K19" s="1">
         <v>1.7</v>
       </c>
-      <c r="K19" s="1">
+      <c r="L19" s="1">
         <v>75.98999999999999</v>
       </c>
-      <c r="L19" t="s">
-        <v>106</v>
-      </c>
-      <c r="M19">
+      <c r="M19" t="s">
+        <v>107</v>
+      </c>
+      <c r="N19">
         <v>0</v>
       </c>
-      <c r="N19" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14">
+      <c r="O19" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15">
       <c r="A20" s="3">
         <v>46226</v>
       </c>
       <c r="B20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D20" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E20" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F20">
         <v>1</v>
       </c>
       <c r="G20" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H20">
         <v>8.289999999999999</v>
@@ -1877,81 +1937,87 @@
       <c r="K20" s="1">
         <v>8.289999999999999</v>
       </c>
-      <c r="L20" t="s">
-        <v>106</v>
-      </c>
-      <c r="M20">
+      <c r="L20" s="1">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="M20" t="s">
+        <v>107</v>
+      </c>
+      <c r="N20">
         <v>0</v>
       </c>
-      <c r="N20" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14">
+      <c r="O20" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15">
       <c r="A21" s="3">
         <v>46226</v>
       </c>
       <c r="B21" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C21" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D21" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E21" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F21">
-        <v>47.01</v>
+        <v>47.006</v>
       </c>
       <c r="G21" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H21">
-        <v>1.61</v>
+        <v>1.588</v>
       </c>
       <c r="I21" s="1">
-        <v>75.69</v>
+        <v>1.608</v>
       </c>
       <c r="J21">
+        <v>75.58564800000001</v>
+      </c>
+      <c r="K21" s="1">
         <v>1.7</v>
       </c>
-      <c r="K21" s="1">
-        <v>79.92</v>
-      </c>
-      <c r="L21" t="s">
-        <v>107</v>
-      </c>
-      <c r="M21">
+      <c r="L21" s="1">
+        <v>79.9102</v>
+      </c>
+      <c r="M21" t="s">
+        <v>108</v>
+      </c>
+      <c r="N21">
         <v>238910</v>
       </c>
-      <c r="N21" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14">
+      <c r="O21" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15">
       <c r="A22" s="3">
         <v>46226</v>
       </c>
       <c r="B22" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C22" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D22" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E22" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F22">
         <v>1</v>
       </c>
       <c r="G22" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H22">
         <v>4.49</v>
@@ -1965,433 +2031,463 @@
       <c r="K22" s="1">
         <v>4.49</v>
       </c>
-      <c r="L22" t="s">
-        <v>107</v>
-      </c>
-      <c r="M22">
+      <c r="L22" s="1">
+        <v>4.49</v>
+      </c>
+      <c r="M22" t="s">
+        <v>108</v>
+      </c>
+      <c r="N22">
         <v>238910</v>
       </c>
-      <c r="N22" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14">
+      <c r="O22" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15">
       <c r="A23" s="3">
         <v>46227</v>
       </c>
       <c r="B23" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D23" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E23" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F23">
         <v>59</v>
       </c>
       <c r="G23" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H23">
-        <v>1.64</v>
+        <v>1.619</v>
       </c>
       <c r="I23" s="1">
-        <v>96.76000000000001</v>
+        <v>1.639</v>
       </c>
       <c r="J23">
+        <v>96.70099999999999</v>
+      </c>
+      <c r="K23" s="1">
         <v>1.7</v>
       </c>
-      <c r="K23" s="1">
+      <c r="L23" s="1">
         <v>100.3</v>
       </c>
-      <c r="L23" t="s">
-        <v>108</v>
-      </c>
-      <c r="M23">
+      <c r="M23" t="s">
+        <v>109</v>
+      </c>
+      <c r="N23">
         <v>391012</v>
       </c>
-      <c r="N23" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14">
+      <c r="O23" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15">
       <c r="A24" s="3">
         <v>46227</v>
       </c>
       <c r="B24" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C24" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D24" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E24" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F24">
-        <v>45.18</v>
+        <v>45.179</v>
       </c>
       <c r="G24" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H24">
-        <v>1.64</v>
+        <v>1.619</v>
       </c>
       <c r="I24" s="1">
-        <v>74.09999999999999</v>
+        <v>1.639</v>
       </c>
       <c r="J24">
+        <v>74.04838100000001</v>
+      </c>
+      <c r="K24" s="1">
         <v>1.73</v>
       </c>
-      <c r="K24" s="1">
-        <v>78.16</v>
-      </c>
-      <c r="L24" t="s">
-        <v>109</v>
-      </c>
-      <c r="M24">
+      <c r="L24" s="1">
+        <v>78.15967000000001</v>
+      </c>
+      <c r="M24" t="s">
+        <v>110</v>
+      </c>
+      <c r="N24">
         <v>49388</v>
       </c>
-      <c r="N24" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14">
+      <c r="O24" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15">
       <c r="A25" s="3">
         <v>46227</v>
       </c>
       <c r="B25" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C25" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D25" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E25" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F25">
-        <v>56.31</v>
+        <v>56.308</v>
       </c>
       <c r="G25" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H25">
-        <v>1.64</v>
+        <v>1.619</v>
       </c>
       <c r="I25" s="1">
-        <v>92.34999999999999</v>
+        <v>1.639</v>
       </c>
       <c r="J25">
+        <v>92.28881199999999</v>
+      </c>
+      <c r="K25" s="1">
         <v>1.72</v>
       </c>
-      <c r="K25" s="1">
-        <v>96.84999999999999</v>
-      </c>
-      <c r="L25" t="s">
-        <v>110</v>
-      </c>
-      <c r="M25">
+      <c r="L25" s="1">
+        <v>96.84976</v>
+      </c>
+      <c r="M25" t="s">
+        <v>111</v>
+      </c>
+      <c r="N25">
         <v>0</v>
       </c>
-      <c r="N25" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14">
+      <c r="O25" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15">
       <c r="A26" s="3">
         <v>46230</v>
       </c>
       <c r="B26" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C26" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D26" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E26" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F26">
         <v>45</v>
       </c>
       <c r="G26" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H26">
-        <v>1.64</v>
+        <v>1.619</v>
       </c>
       <c r="I26" s="1">
-        <v>73.8</v>
+        <v>1.639</v>
       </c>
       <c r="J26">
+        <v>73.755</v>
+      </c>
+      <c r="K26" s="1">
         <v>1.74</v>
       </c>
-      <c r="K26" s="1">
+      <c r="L26" s="1">
         <v>78.3</v>
       </c>
-      <c r="L26" t="s">
-        <v>111</v>
-      </c>
-      <c r="M26">
+      <c r="M26" t="s">
+        <v>112</v>
+      </c>
+      <c r="N26">
         <v>0</v>
       </c>
-      <c r="N26" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14">
+      <c r="O26" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15">
       <c r="A27" s="3">
         <v>46230</v>
       </c>
       <c r="B27" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C27" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D27" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E27" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F27">
         <v>48.42</v>
       </c>
       <c r="G27" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H27">
-        <v>1.64</v>
+        <v>1.619</v>
       </c>
       <c r="I27" s="1">
-        <v>79.41</v>
+        <v>1.639</v>
       </c>
       <c r="J27">
+        <v>79.36038000000001</v>
+      </c>
+      <c r="K27" s="1">
         <v>1.74</v>
       </c>
-      <c r="K27" s="1">
-        <v>84.25</v>
-      </c>
-      <c r="L27" t="s">
-        <v>112</v>
-      </c>
-      <c r="M27">
+      <c r="L27" s="1">
+        <v>84.2508</v>
+      </c>
+      <c r="M27" t="s">
+        <v>113</v>
+      </c>
+      <c r="N27">
         <v>0</v>
       </c>
-      <c r="N27" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14">
+      <c r="O27" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15">
       <c r="A28" s="3">
         <v>46230</v>
       </c>
       <c r="B28" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D28" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E28" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F28">
         <v>40</v>
       </c>
       <c r="G28" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H28">
-        <v>1.64</v>
+        <v>1.619</v>
       </c>
       <c r="I28" s="1">
-        <v>65.59999999999999</v>
+        <v>1.639</v>
       </c>
       <c r="J28">
+        <v>65.56</v>
+      </c>
+      <c r="K28" s="1">
         <v>1.75</v>
       </c>
-      <c r="K28" s="1">
+      <c r="L28" s="1">
         <v>70</v>
       </c>
-      <c r="L28" t="s">
-        <v>113</v>
-      </c>
-      <c r="M28">
+      <c r="M28" t="s">
+        <v>114</v>
+      </c>
+      <c r="N28">
         <v>147973</v>
       </c>
-      <c r="N28" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14">
+      <c r="O28" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15">
       <c r="A29" s="3">
         <v>46230</v>
       </c>
       <c r="B29" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C29" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D29" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E29" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F29">
         <v>39.04</v>
       </c>
       <c r="G29" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H29">
-        <v>1.64</v>
+        <v>1.619</v>
       </c>
       <c r="I29" s="1">
-        <v>64.03</v>
+        <v>1.639</v>
       </c>
       <c r="J29">
+        <v>63.98656</v>
+      </c>
+      <c r="K29" s="1">
         <v>1.76</v>
       </c>
-      <c r="K29" s="1">
-        <v>68.70999999999999</v>
-      </c>
-      <c r="L29" t="s">
-        <v>114</v>
-      </c>
-      <c r="M29">
+      <c r="L29" s="1">
+        <v>68.71040000000001</v>
+      </c>
+      <c r="M29" t="s">
+        <v>115</v>
+      </c>
+      <c r="N29">
         <v>0</v>
       </c>
-      <c r="N29" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14">
+      <c r="O29" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15">
       <c r="A30" s="3">
         <v>46230</v>
       </c>
       <c r="B30" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C30" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D30" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E30" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F30">
         <v>40</v>
       </c>
       <c r="G30" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H30">
-        <v>1.64</v>
+        <v>1.619</v>
       </c>
       <c r="I30" s="1">
-        <v>65.59999999999999</v>
+        <v>1.639</v>
       </c>
       <c r="J30">
+        <v>65.56</v>
+      </c>
+      <c r="K30" s="1">
         <v>1.75</v>
       </c>
-      <c r="K30" s="1">
+      <c r="L30" s="1">
         <v>70</v>
       </c>
-      <c r="L30" t="s">
-        <v>115</v>
-      </c>
-      <c r="M30">
+      <c r="M30" t="s">
+        <v>116</v>
+      </c>
+      <c r="N30">
         <v>417017</v>
       </c>
-      <c r="N30" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14">
+      <c r="O30" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15">
       <c r="A31" s="3">
         <v>46231</v>
       </c>
       <c r="B31" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C31" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D31" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E31" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F31">
         <v>51</v>
       </c>
       <c r="G31" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H31">
-        <v>1.67</v>
+        <v>1.653</v>
       </c>
       <c r="I31" s="1">
-        <v>85.17</v>
+        <v>1.673</v>
       </c>
       <c r="J31">
+        <v>85.32299999999999</v>
+      </c>
+      <c r="K31" s="1">
         <v>1.74</v>
       </c>
-      <c r="K31" s="1">
+      <c r="L31" s="1">
         <v>88.73999999999999</v>
       </c>
-      <c r="L31" t="s">
-        <v>116</v>
-      </c>
-      <c r="M31">
+      <c r="M31" t="s">
+        <v>117</v>
+      </c>
+      <c r="N31">
         <v>471251</v>
       </c>
-      <c r="N31" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14">
+      <c r="O31" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15">
       <c r="A32" s="3">
         <v>46231</v>
       </c>
       <c r="B32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C32" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D32" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E32" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F32">
         <v>1</v>
       </c>
       <c r="G32" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H32">
         <v>4.99</v>
@@ -2405,609 +2501,651 @@
       <c r="K32" s="1">
         <v>4.99</v>
       </c>
-      <c r="L32" t="s">
-        <v>116</v>
-      </c>
-      <c r="M32">
+      <c r="L32" s="1">
+        <v>4.99</v>
+      </c>
+      <c r="M32" t="s">
+        <v>117</v>
+      </c>
+      <c r="N32">
         <v>471251</v>
       </c>
-      <c r="N32" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14">
+      <c r="O32" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15">
       <c r="A33" s="3">
         <v>46231</v>
       </c>
       <c r="B33" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C33" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D33" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E33" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F33">
         <v>37</v>
       </c>
       <c r="G33" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H33">
-        <v>1.67</v>
+        <v>1.653</v>
       </c>
       <c r="I33" s="1">
-        <v>61.79</v>
+        <v>1.673</v>
       </c>
       <c r="J33">
+        <v>61.901</v>
+      </c>
+      <c r="K33" s="1">
         <v>1.75</v>
       </c>
-      <c r="K33" s="1">
+      <c r="L33" s="1">
         <v>64.75</v>
       </c>
-      <c r="L33" t="s">
-        <v>117</v>
-      </c>
-      <c r="M33">
+      <c r="M33" t="s">
+        <v>118</v>
+      </c>
+      <c r="N33">
         <v>0</v>
       </c>
-      <c r="N33" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14">
+      <c r="O33" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15">
       <c r="A34" s="3">
         <v>46232</v>
       </c>
       <c r="B34" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C34" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D34" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E34" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F34">
-        <v>26.7</v>
+        <v>26.703</v>
       </c>
       <c r="G34" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H34">
-        <v>1.69</v>
+        <v>1.674</v>
       </c>
       <c r="I34" s="1">
-        <v>45.12</v>
+        <v>1.694</v>
       </c>
       <c r="J34">
+        <v>45.234882</v>
+      </c>
+      <c r="K34" s="1">
         <v>1.75</v>
       </c>
-      <c r="K34" s="1">
-        <v>46.72</v>
-      </c>
-      <c r="L34" t="s">
-        <v>118</v>
-      </c>
-      <c r="M34">
+      <c r="L34" s="1">
+        <v>46.73025</v>
+      </c>
+      <c r="M34" t="s">
+        <v>119</v>
+      </c>
+      <c r="N34">
         <v>0</v>
       </c>
-      <c r="N34" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14">
+      <c r="O34" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15">
       <c r="A35" s="3">
         <v>46232</v>
       </c>
       <c r="B35" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C35" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D35" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E35" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F35">
         <v>39.84</v>
       </c>
       <c r="G35" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H35">
-        <v>1.69</v>
+        <v>1.674</v>
       </c>
       <c r="I35" s="1">
-        <v>67.33</v>
+        <v>1.694</v>
       </c>
       <c r="J35">
+        <v>67.48896000000001</v>
+      </c>
+      <c r="K35" s="1">
         <v>1.75</v>
       </c>
-      <c r="K35" s="1">
+      <c r="L35" s="1">
         <v>69.72</v>
       </c>
-      <c r="L35" t="s">
-        <v>119</v>
-      </c>
-      <c r="M35">
+      <c r="M35" t="s">
+        <v>120</v>
+      </c>
+      <c r="N35">
         <v>339177</v>
       </c>
-      <c r="N35" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14">
+      <c r="O35" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15">
       <c r="A36" s="3">
         <v>46232</v>
       </c>
       <c r="B36" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C36" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D36" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E36" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F36">
         <v>55.88</v>
       </c>
       <c r="G36" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H36">
-        <v>1.69</v>
+        <v>1.674</v>
       </c>
       <c r="I36" s="1">
-        <v>94.44</v>
+        <v>1.694</v>
       </c>
       <c r="J36">
+        <v>94.66072</v>
+      </c>
+      <c r="K36" s="1">
         <v>1.75</v>
       </c>
-      <c r="K36" s="1">
+      <c r="L36" s="1">
         <v>97.79000000000001</v>
       </c>
-      <c r="L36" t="s">
-        <v>120</v>
-      </c>
-      <c r="M36">
+      <c r="M36" t="s">
+        <v>121</v>
+      </c>
+      <c r="N36">
         <v>0</v>
       </c>
-      <c r="N36" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14">
+      <c r="O36" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15">
       <c r="A37" s="3">
         <v>46233</v>
       </c>
       <c r="B37" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C37" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D37" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E37" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F37">
         <v>42.21</v>
       </c>
       <c r="G37" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H37">
-        <v>1.69</v>
+        <v>1.674</v>
       </c>
       <c r="I37" s="1">
-        <v>71.33</v>
+        <v>1.694</v>
       </c>
       <c r="J37">
+        <v>71.50373999999999</v>
+      </c>
+      <c r="K37" s="1">
         <v>1.76</v>
       </c>
-      <c r="K37" s="1">
-        <v>74.29000000000001</v>
-      </c>
-      <c r="L37" t="s">
-        <v>121</v>
-      </c>
-      <c r="M37">
+      <c r="L37" s="1">
+        <v>74.28959999999999</v>
+      </c>
+      <c r="M37" t="s">
+        <v>122</v>
+      </c>
+      <c r="N37">
         <v>229700</v>
       </c>
-      <c r="N37" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14">
+      <c r="O37" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15">
       <c r="A38" s="3">
         <v>46233</v>
       </c>
       <c r="B38" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C38" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D38" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E38" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F38">
-        <v>40.82</v>
+        <v>40.817</v>
       </c>
       <c r="G38" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H38">
         <v>2.02</v>
       </c>
       <c r="I38" s="1">
-        <v>82.45999999999999</v>
+        <v>2.02</v>
       </c>
       <c r="J38">
+        <v>82.45034</v>
+      </c>
+      <c r="K38" s="1">
         <v>2.02</v>
       </c>
-      <c r="K38" s="1">
-        <v>82.45999999999999</v>
-      </c>
-      <c r="L38" t="s">
-        <v>122</v>
-      </c>
-      <c r="M38">
+      <c r="L38" s="1">
+        <v>82.45034</v>
+      </c>
+      <c r="M38" t="s">
+        <v>123</v>
+      </c>
+      <c r="N38">
         <v>14825</v>
       </c>
-      <c r="N38" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14">
+      <c r="O38" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15">
       <c r="A39" s="3">
         <v>46233</v>
       </c>
       <c r="B39" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C39" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D39" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E39" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F39">
         <v>44</v>
       </c>
       <c r="G39" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H39">
-        <v>1.47</v>
+        <v>1.449</v>
       </c>
       <c r="I39" s="1">
-        <v>64.68000000000001</v>
+        <v>1.469</v>
       </c>
       <c r="J39">
+        <v>64.636</v>
+      </c>
+      <c r="K39" s="1">
         <v>1.55</v>
       </c>
-      <c r="K39" s="1">
+      <c r="L39" s="1">
         <v>68.2</v>
       </c>
-      <c r="L39" t="s">
-        <v>123</v>
-      </c>
-      <c r="M39">
+      <c r="M39" t="s">
+        <v>124</v>
+      </c>
+      <c r="N39">
         <v>0</v>
       </c>
-      <c r="N39" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14">
+      <c r="O39" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15">
       <c r="A40" s="3">
         <v>46233</v>
       </c>
       <c r="B40" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C40" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D40" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E40" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F40">
-        <v>43.36</v>
+        <v>43.358</v>
       </c>
       <c r="G40" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H40">
-        <v>1.69</v>
+        <v>1.674</v>
       </c>
       <c r="I40" s="1">
-        <v>73.28</v>
+        <v>1.694</v>
       </c>
       <c r="J40">
+        <v>73.448452</v>
+      </c>
+      <c r="K40" s="1">
         <v>1.76</v>
       </c>
-      <c r="K40" s="1">
-        <v>76.31</v>
-      </c>
-      <c r="L40" t="s">
-        <v>124</v>
-      </c>
-      <c r="M40">
+      <c r="L40" s="1">
+        <v>76.31008</v>
+      </c>
+      <c r="M40" t="s">
+        <v>125</v>
+      </c>
+      <c r="N40">
         <v>0</v>
       </c>
-      <c r="N40" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14">
+      <c r="O40" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15">
       <c r="A41" s="3">
         <v>46233</v>
       </c>
       <c r="B41" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C41" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D41" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E41" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F41">
-        <v>18.18</v>
+        <v>18.182</v>
       </c>
       <c r="G41" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H41">
-        <v>1.69</v>
+        <v>1.674</v>
       </c>
       <c r="I41" s="1">
-        <v>30.72</v>
+        <v>1.694</v>
       </c>
       <c r="J41">
+        <v>30.800308</v>
+      </c>
+      <c r="K41" s="1">
         <v>1.76</v>
       </c>
-      <c r="K41" s="1">
-        <v>32</v>
-      </c>
-      <c r="L41" t="s">
-        <v>125</v>
-      </c>
-      <c r="M41">
+      <c r="L41" s="1">
+        <v>32.00032</v>
+      </c>
+      <c r="M41" t="s">
+        <v>126</v>
+      </c>
+      <c r="N41">
         <v>393583</v>
       </c>
-      <c r="N41" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14">
+      <c r="O41" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15">
       <c r="A42" s="3">
         <v>46234</v>
       </c>
       <c r="B42" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C42" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D42" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E42" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F42">
         <v>35</v>
       </c>
       <c r="G42" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H42">
-        <v>1.71</v>
+        <v>1.689</v>
       </c>
       <c r="I42" s="1">
-        <v>59.85</v>
+        <v>1.709</v>
       </c>
       <c r="J42">
+        <v>59.815</v>
+      </c>
+      <c r="K42" s="1">
         <v>1.77</v>
       </c>
-      <c r="K42" s="1">
+      <c r="L42" s="1">
         <v>61.95</v>
       </c>
-      <c r="L42" t="s">
-        <v>126</v>
-      </c>
-      <c r="M42">
+      <c r="M42" t="s">
+        <v>127</v>
+      </c>
+      <c r="N42">
         <v>471900</v>
       </c>
-      <c r="N42" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="43" spans="1:14">
+      <c r="O42" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15">
       <c r="A43" s="3">
         <v>46234</v>
       </c>
       <c r="B43" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C43" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D43" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E43" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F43">
         <v>42</v>
       </c>
       <c r="G43" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H43">
-        <v>1.71</v>
+        <v>1.689</v>
       </c>
       <c r="I43" s="1">
-        <v>71.81999999999999</v>
+        <v>1.709</v>
       </c>
       <c r="J43">
+        <v>71.77800000000001</v>
+      </c>
+      <c r="K43" s="1">
         <v>1.77</v>
       </c>
-      <c r="K43" s="1">
+      <c r="L43" s="1">
         <v>74.34</v>
       </c>
-      <c r="L43" t="s">
-        <v>127</v>
-      </c>
-      <c r="M43">
+      <c r="M43" t="s">
+        <v>128</v>
+      </c>
+      <c r="N43">
         <v>0</v>
       </c>
-      <c r="N43" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14">
+      <c r="O43" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15">
       <c r="A44" s="3">
         <v>46234</v>
       </c>
       <c r="B44" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C44" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D44" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E44" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F44">
         <v>12</v>
       </c>
       <c r="G44" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H44">
-        <v>1.71</v>
+        <v>1.689</v>
       </c>
       <c r="I44" s="1">
-        <v>20.52</v>
+        <v>1.709</v>
       </c>
       <c r="J44">
+        <v>20.508</v>
+      </c>
+      <c r="K44" s="1">
         <v>1.77</v>
       </c>
-      <c r="K44" s="1">
+      <c r="L44" s="1">
         <v>21.24</v>
       </c>
-      <c r="L44" t="s">
-        <v>128</v>
-      </c>
-      <c r="M44">
+      <c r="M44" t="s">
+        <v>129</v>
+      </c>
+      <c r="N44">
         <v>0</v>
       </c>
-      <c r="N44" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14">
+      <c r="O44" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15">
       <c r="A45" s="3">
         <v>46234</v>
       </c>
       <c r="B45" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C45" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D45" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E45" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F45">
-        <v>41.3</v>
+        <v>41.299</v>
       </c>
       <c r="G45" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H45">
-        <v>1.71</v>
+        <v>1.689</v>
       </c>
       <c r="I45" s="1">
-        <v>70.62</v>
+        <v>1.709</v>
       </c>
       <c r="J45">
+        <v>70.57999100000001</v>
+      </c>
+      <c r="K45" s="1">
         <v>1.77</v>
       </c>
-      <c r="K45" s="1">
-        <v>73.09999999999999</v>
-      </c>
-      <c r="L45" t="s">
-        <v>129</v>
-      </c>
-      <c r="M45">
+      <c r="L45" s="1">
+        <v>73.09923000000001</v>
+      </c>
+      <c r="M45" t="s">
+        <v>130</v>
+      </c>
+      <c r="N45">
         <v>0</v>
       </c>
-      <c r="N45" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="46" spans="1:14">
+      <c r="O45" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15">
       <c r="A46" s="3">
         <v>46234</v>
       </c>
       <c r="B46" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C46" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D46" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E46" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F46">
         <v>1</v>
       </c>
       <c r="G46" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H46">
         <v>3.52</v>
@@ -3021,37 +3159,40 @@
       <c r="K46" s="1">
         <v>3.52</v>
       </c>
-      <c r="L46" t="s">
-        <v>129</v>
-      </c>
-      <c r="M46">
+      <c r="L46" s="1">
+        <v>3.52</v>
+      </c>
+      <c r="M46" t="s">
+        <v>130</v>
+      </c>
+      <c r="N46">
         <v>0</v>
       </c>
-      <c r="N46" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="47" spans="1:14">
+      <c r="O46" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15">
       <c r="A47" s="3">
         <v>46234</v>
       </c>
       <c r="B47" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C47" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D47" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E47" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F47">
         <v>1</v>
       </c>
       <c r="G47" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H47">
         <v>9.390000000000001</v>
@@ -3065,371 +3206,398 @@
       <c r="K47" s="1">
         <v>9.390000000000001</v>
       </c>
-      <c r="L47" t="s">
-        <v>129</v>
-      </c>
-      <c r="M47">
+      <c r="L47" s="1">
+        <v>9.390000000000001</v>
+      </c>
+      <c r="M47" t="s">
+        <v>130</v>
+      </c>
+      <c r="N47">
         <v>0</v>
       </c>
-      <c r="N47" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="48" spans="1:14">
+      <c r="O47" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15">
       <c r="A48" s="3">
         <v>46234</v>
       </c>
       <c r="B48" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C48" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D48" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E48" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F48">
-        <v>49.5</v>
+        <v>49.497</v>
       </c>
       <c r="G48" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H48">
-        <v>1.71</v>
+        <v>1.689</v>
       </c>
       <c r="I48" s="1">
-        <v>84.64</v>
+        <v>1.709</v>
       </c>
       <c r="J48">
+        <v>84.590373</v>
+      </c>
+      <c r="K48" s="1">
         <v>1.77</v>
       </c>
-      <c r="K48" s="1">
-        <v>87.62</v>
-      </c>
-      <c r="L48" t="s">
-        <v>130</v>
-      </c>
-      <c r="M48">
+      <c r="L48" s="1">
+        <v>87.60969</v>
+      </c>
+      <c r="M48" t="s">
+        <v>131</v>
+      </c>
+      <c r="N48">
         <v>239890</v>
       </c>
-      <c r="N48" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="49" spans="1:14">
+      <c r="O48" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15">
       <c r="A49" s="3">
         <v>46234</v>
       </c>
       <c r="B49" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C49" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D49" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E49" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F49">
         <v>35</v>
       </c>
       <c r="G49" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H49">
-        <v>1.71</v>
+        <v>1.689</v>
       </c>
       <c r="I49" s="1">
-        <v>59.85</v>
+        <v>1.709</v>
       </c>
       <c r="J49">
+        <v>59.815</v>
+      </c>
+      <c r="K49" s="1">
         <v>1.76</v>
       </c>
-      <c r="K49" s="1">
+      <c r="L49" s="1">
         <v>61.6</v>
       </c>
-      <c r="L49" t="s">
-        <v>131</v>
-      </c>
-      <c r="M49">
+      <c r="M49" t="s">
+        <v>132</v>
+      </c>
+      <c r="N49">
         <v>576900</v>
       </c>
-      <c r="N49" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="50" spans="1:14">
+      <c r="O49" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15">
       <c r="A50" s="3">
         <v>46234</v>
       </c>
       <c r="B50" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C50" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D50" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E50" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F50">
         <v>42</v>
       </c>
       <c r="G50" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H50">
-        <v>1.71</v>
+        <v>1.689</v>
       </c>
       <c r="I50" s="1">
-        <v>71.81999999999999</v>
+        <v>1.709</v>
       </c>
       <c r="J50">
+        <v>71.77800000000001</v>
+      </c>
+      <c r="K50" s="1">
         <v>1.78</v>
       </c>
-      <c r="K50" s="1">
+      <c r="L50" s="1">
         <v>74.76000000000001</v>
       </c>
-      <c r="L50" t="s">
-        <v>132</v>
-      </c>
-      <c r="M50">
+      <c r="M50" t="s">
+        <v>133</v>
+      </c>
+      <c r="N50">
         <v>176276</v>
       </c>
-      <c r="N50" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="51" spans="1:14">
+      <c r="O50" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15">
       <c r="A51" s="3">
         <v>46234</v>
       </c>
       <c r="B51" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C51" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D51" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E51" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F51">
-        <v>48.6</v>
+        <v>48.599</v>
       </c>
       <c r="G51" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H51">
-        <v>1.71</v>
+        <v>1.689</v>
       </c>
       <c r="I51" s="1">
-        <v>83.11</v>
+        <v>1.709</v>
       </c>
       <c r="J51">
+        <v>83.055691</v>
+      </c>
+      <c r="K51" s="1">
         <v>1.77</v>
       </c>
-      <c r="K51" s="1">
-        <v>86.02</v>
-      </c>
-      <c r="L51" t="s">
-        <v>133</v>
-      </c>
-      <c r="M51">
+      <c r="L51" s="1">
+        <v>86.02023</v>
+      </c>
+      <c r="M51" t="s">
+        <v>134</v>
+      </c>
+      <c r="N51">
         <v>0</v>
       </c>
-      <c r="N51" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="52" spans="1:14">
+      <c r="O51" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15">
       <c r="A52" s="3">
         <v>46234</v>
       </c>
       <c r="B52" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C52" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D52" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E52" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F52">
-        <v>39.67</v>
+        <v>39.672</v>
       </c>
       <c r="G52" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H52">
-        <v>1.71</v>
+        <v>1.689</v>
       </c>
       <c r="I52" s="1">
-        <v>67.84</v>
+        <v>1.709</v>
       </c>
       <c r="J52">
+        <v>67.799448</v>
+      </c>
+      <c r="K52" s="1">
         <v>1.77</v>
       </c>
-      <c r="K52" s="1">
-        <v>70.22</v>
-      </c>
-      <c r="L52" t="s">
-        <v>134</v>
-      </c>
-      <c r="M52">
+      <c r="L52" s="1">
+        <v>70.21944000000001</v>
+      </c>
+      <c r="M52" t="s">
+        <v>135</v>
+      </c>
+      <c r="N52">
         <v>165568</v>
       </c>
-      <c r="N52" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="53" spans="1:14">
+      <c r="O52" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15">
       <c r="A53" s="3">
         <v>46234</v>
       </c>
       <c r="B53" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C53" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D53" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E53" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F53">
         <v>12.65</v>
       </c>
       <c r="G53" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H53">
-        <v>1.71</v>
+        <v>1.689</v>
       </c>
       <c r="I53" s="1">
-        <v>21.63</v>
+        <v>1.709</v>
       </c>
       <c r="J53">
+        <v>21.61885</v>
+      </c>
+      <c r="K53" s="1">
         <v>1.77</v>
       </c>
-      <c r="K53" s="1">
-        <v>22.39</v>
-      </c>
-      <c r="L53" t="s">
-        <v>135</v>
-      </c>
-      <c r="M53">
+      <c r="L53" s="1">
+        <v>22.3905</v>
+      </c>
+      <c r="M53" t="s">
+        <v>136</v>
+      </c>
+      <c r="N53">
         <v>165960</v>
       </c>
-      <c r="N53" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="54" spans="1:14">
+      <c r="O53" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15">
       <c r="A54" s="3">
         <v>46234</v>
       </c>
       <c r="B54" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C54" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D54" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E54" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F54">
         <v>47.23</v>
       </c>
       <c r="G54" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H54">
-        <v>1.71</v>
+        <v>1.689</v>
       </c>
       <c r="I54" s="1">
-        <v>80.76000000000001</v>
+        <v>1.709</v>
       </c>
       <c r="J54">
+        <v>80.71607</v>
+      </c>
+      <c r="K54" s="1">
         <v>1.78</v>
       </c>
-      <c r="K54" s="1">
-        <v>84.06999999999999</v>
-      </c>
-      <c r="L54" t="s">
-        <v>104</v>
-      </c>
-      <c r="M54">
+      <c r="L54" s="1">
+        <v>84.0694</v>
+      </c>
+      <c r="M54" t="s">
+        <v>105</v>
+      </c>
+      <c r="N54">
         <v>421577</v>
       </c>
-      <c r="N54" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="55" spans="1:14">
+      <c r="O54" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15">
       <c r="A55" s="3">
         <v>46234</v>
       </c>
       <c r="B55" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C55" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D55" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E55" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F55">
-        <v>20.01</v>
+        <v>20.011</v>
       </c>
       <c r="G55" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H55">
-        <v>1.71</v>
+        <v>1.689</v>
       </c>
       <c r="I55" s="1">
-        <v>34.22</v>
+        <v>1.709</v>
       </c>
       <c r="J55">
+        <v>34.198799</v>
+      </c>
+      <c r="K55" s="1">
         <v>1.78</v>
       </c>
-      <c r="K55" s="1">
-        <v>35.62</v>
-      </c>
-      <c r="L55" t="s">
-        <v>136</v>
-      </c>
-      <c r="M55">
+      <c r="L55" s="1">
+        <v>35.61958</v>
+      </c>
+      <c r="M55" t="s">
+        <v>137</v>
+      </c>
+      <c r="N55">
         <v>0</v>
       </c>
-      <c r="N55" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="58" spans="1:14">
+      <c r="O55" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15">
       <c r="A58" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B58" s="4"/>
       <c r="C58" s="4"/>
@@ -3437,49 +3605,49 @@
       <c r="E58" s="4"/>
       <c r="F58" s="4"/>
     </row>
-    <row r="59" spans="1:14">
+    <row r="59" spans="1:15">
       <c r="A59" s="5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="60" spans="1:14">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15">
       <c r="A60" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B60" s="7">
-        <v>1994.16</v>
+        <v>1994.159</v>
       </c>
       <c r="C60" s="7">
         <v>46</v>
       </c>
       <c r="D60" s="8">
-        <v>1.633279</v>
+        <v>1.633079</v>
       </c>
       <c r="E60" s="7">
-        <v>3257.02</v>
+        <v>3256.62</v>
       </c>
       <c r="F60" s="7">
         <v>3422.75</v>
       </c>
     </row>
-    <row r="61" spans="1:14">
+    <row r="61" spans="1:15">
       <c r="A61" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B61" s="7">
         <v>44</v>
@@ -3488,38 +3656,38 @@
         <v>1</v>
       </c>
       <c r="D61" s="8">
-        <v>1.47</v>
+        <v>1.469</v>
       </c>
       <c r="E61" s="7">
-        <v>64.68000000000001</v>
+        <v>64.64</v>
       </c>
       <c r="F61" s="7">
         <v>68.2</v>
       </c>
     </row>
-    <row r="62" spans="1:14">
+    <row r="62" spans="1:15">
       <c r="A62" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B62" s="7">
-        <v>40.82</v>
+        <v>40.817</v>
       </c>
       <c r="C62" s="7">
         <v>1</v>
       </c>
       <c r="D62" s="8">
-        <v>2.020088</v>
+        <v>2.02</v>
       </c>
       <c r="E62" s="7">
-        <v>82.45999999999999</v>
+        <v>82.45</v>
       </c>
       <c r="F62" s="7">
-        <v>82.45999999999999</v>
-      </c>
-    </row>
-    <row r="63" spans="1:14">
+        <v>82.45</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15">
       <c r="A63" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B63" s="7">
         <v>2</v>
@@ -3537,9 +3705,9 @@
         <v>9.48</v>
       </c>
     </row>
-    <row r="64" spans="1:14">
+    <row r="64" spans="1:15">
       <c r="A64" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B64" s="7">
         <v>1</v>
@@ -3559,7 +3727,7 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B65" s="7">
         <v>1</v>
@@ -3579,7 +3747,7 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B66" s="7">
         <v>1</v>
@@ -3599,7 +3767,7 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B67" s="7">
         <v>1</v>
@@ -3619,20 +3787,20 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B68" s="10">
-        <v>2084.98</v>
+        <v>2084.976</v>
       </c>
       <c r="C68" s="10">
         <v>54</v>
       </c>
       <c r="D68" s="8"/>
       <c r="E68" s="10">
-        <v>3435.86</v>
+        <v>3435.41</v>
       </c>
       <c r="F68" s="10">
-        <v>3605.11</v>
+        <v>3605.1</v>
       </c>
     </row>
   </sheetData>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/МЕРКУРИЙ ПРОИЗВОДСТВО И ПАКЕТАЖ АД/МЕРКУРИЙ ПРОИЗВОДСТВО И ПАКЕТАЖ АД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/МЕРКУРИЙ ПРОИЗВОДСТВО И ПАКЕТАЖ АД/МЕРКУРИЙ ПРОИЗВОДСТВО И ПАКЕТАЖ АД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="191">
   <si>
     <t>Дата</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Тип количество</t>
-  </si>
-  <si>
-    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -597,9 +594,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -693,10 +690,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -991,7 +988,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O68"/>
+  <dimension ref="A1:N68"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -1004,13 +1001,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1053,736 +1050,688 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15">
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
         <v>46219</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F2">
         <v>44.663</v>
       </c>
       <c r="G2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H2">
-        <v>1.499</v>
+        <v>1.519</v>
       </c>
       <c r="I2" s="1">
-        <v>1.519</v>
+        <v>67.843</v>
       </c>
       <c r="J2">
-        <v>67.843097</v>
+        <v>1.6</v>
       </c>
       <c r="K2" s="1">
-        <v>1.6</v>
-      </c>
-      <c r="L2" s="1">
-        <v>71.46080000000001</v>
-      </c>
-      <c r="M2" t="s">
-        <v>91</v>
-      </c>
-      <c r="N2">
+        <v>71.461</v>
+      </c>
+      <c r="L2" t="s">
+        <v>90</v>
+      </c>
+      <c r="M2">
         <v>420393</v>
       </c>
-      <c r="O2" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+      <c r="N2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="3">
         <v>46219</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F3">
         <v>43.789</v>
       </c>
       <c r="G3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H3">
-        <v>1.499</v>
+        <v>1.519</v>
       </c>
       <c r="I3" s="1">
-        <v>1.519</v>
+        <v>66.515</v>
       </c>
       <c r="J3">
-        <v>66.515491</v>
+        <v>1.61</v>
       </c>
       <c r="K3" s="1">
-        <v>1.61</v>
-      </c>
-      <c r="L3" s="1">
-        <v>70.50029000000001</v>
-      </c>
-      <c r="M3" t="s">
-        <v>92</v>
-      </c>
-      <c r="N3">
+        <v>70.5</v>
+      </c>
+      <c r="L3" t="s">
+        <v>91</v>
+      </c>
+      <c r="M3">
         <v>0</v>
       </c>
-      <c r="O3" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+      <c r="N3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="3">
         <v>46219</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F4">
         <v>41.84</v>
       </c>
       <c r="G4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H4">
-        <v>1.499</v>
+        <v>1.519</v>
       </c>
       <c r="I4" s="1">
-        <v>1.519</v>
+        <v>63.555</v>
       </c>
       <c r="J4">
-        <v>63.55496</v>
+        <v>1.62</v>
       </c>
       <c r="K4" s="1">
-        <v>1.62</v>
-      </c>
-      <c r="L4" s="1">
-        <v>67.7808</v>
-      </c>
-      <c r="M4" t="s">
-        <v>93</v>
-      </c>
-      <c r="N4">
+        <v>67.78100000000001</v>
+      </c>
+      <c r="L4" t="s">
+        <v>92</v>
+      </c>
+      <c r="M4">
         <v>238082</v>
       </c>
-      <c r="O4" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+      <c r="N4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="3">
         <v>46220</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F5">
         <v>43</v>
       </c>
       <c r="G5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H5">
-        <v>1.499</v>
+        <v>1.519</v>
       </c>
       <c r="I5" s="1">
-        <v>1.519</v>
+        <v>65.31699999999999</v>
       </c>
       <c r="J5">
-        <v>65.31699999999999</v>
+        <v>1.62</v>
       </c>
       <c r="K5" s="1">
-        <v>1.62</v>
-      </c>
-      <c r="L5" s="1">
         <v>69.66</v>
       </c>
-      <c r="M5" t="s">
-        <v>94</v>
-      </c>
-      <c r="N5">
+      <c r="L5" t="s">
+        <v>93</v>
+      </c>
+      <c r="M5">
         <v>470400</v>
       </c>
-      <c r="O5" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+      <c r="N5" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" s="3">
         <v>46220</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F6">
         <v>45.209</v>
       </c>
       <c r="G6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H6">
-        <v>1.499</v>
+        <v>1.519</v>
       </c>
       <c r="I6" s="1">
-        <v>1.519</v>
+        <v>68.672</v>
       </c>
       <c r="J6">
-        <v>68.672471</v>
+        <v>1.63</v>
       </c>
       <c r="K6" s="1">
-        <v>1.63</v>
-      </c>
-      <c r="L6" s="1">
-        <v>73.69067</v>
-      </c>
-      <c r="M6" t="s">
-        <v>95</v>
-      </c>
-      <c r="N6">
+        <v>73.691</v>
+      </c>
+      <c r="L6" t="s">
+        <v>94</v>
+      </c>
+      <c r="M6">
         <v>175575</v>
       </c>
-      <c r="O6" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+      <c r="N6" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" s="3">
         <v>46223</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F7">
         <v>43</v>
       </c>
       <c r="G7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H7">
-        <v>1.546</v>
+        <v>1.566</v>
       </c>
       <c r="I7" s="1">
-        <v>1.566</v>
+        <v>67.33799999999999</v>
       </c>
       <c r="J7">
-        <v>67.33799999999999</v>
+        <v>1.67</v>
       </c>
       <c r="K7" s="1">
-        <v>1.67</v>
-      </c>
-      <c r="L7" s="1">
         <v>71.81</v>
       </c>
-      <c r="M7" t="s">
-        <v>96</v>
-      </c>
-      <c r="N7">
+      <c r="L7" t="s">
+        <v>95</v>
+      </c>
+      <c r="M7">
         <v>0</v>
       </c>
-      <c r="O7" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
+      <c r="N7" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" s="3">
         <v>46223</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F8">
         <v>43.03</v>
       </c>
       <c r="G8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H8">
-        <v>1.546</v>
+        <v>1.566</v>
       </c>
       <c r="I8" s="1">
-        <v>1.566</v>
+        <v>67.38500000000001</v>
       </c>
       <c r="J8">
-        <v>67.38498</v>
+        <v>1.68</v>
       </c>
       <c r="K8" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L8" s="1">
-        <v>72.29040000000001</v>
-      </c>
-      <c r="M8" t="s">
-        <v>97</v>
-      </c>
-      <c r="N8">
+        <v>72.29000000000001</v>
+      </c>
+      <c r="L8" t="s">
+        <v>96</v>
+      </c>
+      <c r="M8">
         <v>0</v>
       </c>
-      <c r="O8" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
+      <c r="N8" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" s="3">
         <v>46223</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F9">
         <v>55</v>
       </c>
       <c r="G9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H9">
-        <v>1.546</v>
+        <v>1.566</v>
       </c>
       <c r="I9" s="1">
-        <v>1.566</v>
+        <v>86.13</v>
       </c>
       <c r="J9">
-        <v>86.13</v>
+        <v>1.68</v>
       </c>
       <c r="K9" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L9" s="1">
         <v>92.40000000000001</v>
       </c>
-      <c r="M9" t="s">
-        <v>98</v>
-      </c>
-      <c r="N9">
+      <c r="L9" t="s">
+        <v>97</v>
+      </c>
+      <c r="M9">
         <v>576340</v>
       </c>
-      <c r="O9" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
+      <c r="N9" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" s="3">
         <v>46224</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F10">
         <v>37</v>
       </c>
       <c r="G10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H10">
-        <v>1.564</v>
+        <v>1.584</v>
       </c>
       <c r="I10" s="1">
-        <v>1.584</v>
+        <v>58.608</v>
       </c>
       <c r="J10">
-        <v>58.608</v>
+        <v>1.68</v>
       </c>
       <c r="K10" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L10" s="1">
         <v>62.16</v>
       </c>
-      <c r="M10" t="s">
-        <v>99</v>
-      </c>
-      <c r="N10">
+      <c r="L10" t="s">
+        <v>98</v>
+      </c>
+      <c r="M10">
         <v>0</v>
       </c>
-      <c r="O10" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
+      <c r="N10" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" s="3">
         <v>46224</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F11">
         <v>62.202</v>
       </c>
       <c r="G11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H11">
-        <v>1.564</v>
+        <v>1.584</v>
       </c>
       <c r="I11" s="1">
-        <v>1.584</v>
+        <v>98.52800000000001</v>
       </c>
       <c r="J11">
-        <v>98.527968</v>
+        <v>1.68</v>
       </c>
       <c r="K11" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L11" s="1">
-        <v>104.49936</v>
-      </c>
-      <c r="M11" t="s">
-        <v>100</v>
-      </c>
-      <c r="N11">
+        <v>104.499</v>
+      </c>
+      <c r="L11" t="s">
+        <v>99</v>
+      </c>
+      <c r="M11">
         <v>0</v>
       </c>
-      <c r="O11" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
+      <c r="N11" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" s="3">
         <v>46224</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D12" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F12">
         <v>78.792</v>
       </c>
       <c r="G12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H12">
-        <v>1.564</v>
+        <v>1.584</v>
       </c>
       <c r="I12" s="1">
-        <v>1.584</v>
+        <v>124.807</v>
       </c>
       <c r="J12">
-        <v>124.806528</v>
+        <v>1.68</v>
       </c>
       <c r="K12" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L12" s="1">
-        <v>132.37056</v>
-      </c>
-      <c r="M12" t="s">
-        <v>101</v>
-      </c>
-      <c r="N12">
+        <v>132.371</v>
+      </c>
+      <c r="L12" t="s">
+        <v>100</v>
+      </c>
+      <c r="M12">
         <v>0</v>
       </c>
-      <c r="O12" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
+      <c r="N12" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" s="3">
         <v>46225</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D13" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F13">
         <v>40</v>
       </c>
       <c r="G13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H13">
-        <v>1.588</v>
+        <v>1.608</v>
       </c>
       <c r="I13" s="1">
-        <v>1.608</v>
+        <v>64.31999999999999</v>
       </c>
       <c r="J13">
-        <v>64.31999999999999</v>
+        <v>1.69</v>
       </c>
       <c r="K13" s="1">
-        <v>1.69</v>
-      </c>
-      <c r="L13" s="1">
         <v>67.59999999999999</v>
       </c>
-      <c r="M13" t="s">
-        <v>102</v>
-      </c>
-      <c r="N13">
+      <c r="L13" t="s">
+        <v>101</v>
+      </c>
+      <c r="M13">
         <v>228700</v>
       </c>
-      <c r="O13" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15">
+      <c r="N13" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" s="3">
         <v>46225</v>
       </c>
       <c r="B14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D14" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E14" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F14">
         <v>50.343</v>
       </c>
       <c r="G14" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H14">
-        <v>1.588</v>
+        <v>1.608</v>
       </c>
       <c r="I14" s="1">
-        <v>1.608</v>
+        <v>80.952</v>
       </c>
       <c r="J14">
-        <v>80.951544</v>
+        <v>1.69</v>
       </c>
       <c r="K14" s="1">
-        <v>1.69</v>
-      </c>
-      <c r="L14" s="1">
-        <v>85.07966999999999</v>
-      </c>
-      <c r="M14" t="s">
-        <v>103</v>
-      </c>
-      <c r="N14">
+        <v>85.08</v>
+      </c>
+      <c r="L14" t="s">
+        <v>102</v>
+      </c>
+      <c r="M14">
         <v>421251</v>
       </c>
-      <c r="O14" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15">
+      <c r="N14" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" s="3">
         <v>46225</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F15">
         <v>53.089</v>
       </c>
       <c r="G15" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H15">
-        <v>1.588</v>
+        <v>1.608</v>
       </c>
       <c r="I15" s="1">
-        <v>1.608</v>
+        <v>85.367</v>
       </c>
       <c r="J15">
-        <v>85.36711200000001</v>
+        <v>1.69</v>
       </c>
       <c r="K15" s="1">
-        <v>1.69</v>
-      </c>
-      <c r="L15" s="1">
-        <v>89.72041</v>
-      </c>
-      <c r="M15" t="s">
-        <v>104</v>
-      </c>
-      <c r="N15">
+        <v>89.72</v>
+      </c>
+      <c r="L15" t="s">
+        <v>103</v>
+      </c>
+      <c r="M15">
         <v>420909</v>
       </c>
-      <c r="O15" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15">
+      <c r="N15" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" s="3">
         <v>46225</v>
       </c>
       <c r="B16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C16" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D16" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F16">
         <v>59.2</v>
       </c>
       <c r="G16" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H16">
-        <v>1.588</v>
+        <v>1.608</v>
       </c>
       <c r="I16" s="1">
-        <v>1.608</v>
+        <v>95.194</v>
       </c>
       <c r="J16">
-        <v>95.1936</v>
+        <v>1.7</v>
       </c>
       <c r="K16" s="1">
-        <v>1.7</v>
-      </c>
-      <c r="L16" s="1">
         <v>100.64</v>
       </c>
-      <c r="M16" t="s">
-        <v>105</v>
-      </c>
-      <c r="N16">
+      <c r="L16" t="s">
+        <v>104</v>
+      </c>
+      <c r="M16">
         <v>0</v>
       </c>
-      <c r="O16" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15">
+      <c r="N16" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" s="3">
         <v>46225</v>
       </c>
       <c r="B17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C17" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E17" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F17">
         <v>1</v>
       </c>
       <c r="G17" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H17">
         <v>1.02</v>
@@ -1796,134 +1745,125 @@
       <c r="K17" s="1">
         <v>1.02</v>
       </c>
-      <c r="L17" s="1">
-        <v>1.02</v>
-      </c>
-      <c r="M17" t="s">
-        <v>105</v>
-      </c>
-      <c r="N17">
+      <c r="L17" t="s">
+        <v>104</v>
+      </c>
+      <c r="M17">
         <v>0</v>
       </c>
-      <c r="O17" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15">
+      <c r="N17" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18" s="3">
         <v>46225</v>
       </c>
       <c r="B18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D18" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E18" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F18">
         <v>50.218</v>
       </c>
       <c r="G18" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H18">
-        <v>1.588</v>
+        <v>1.608</v>
       </c>
       <c r="I18" s="1">
-        <v>1.608</v>
+        <v>80.751</v>
       </c>
       <c r="J18">
-        <v>80.750544</v>
+        <v>1.7</v>
       </c>
       <c r="K18" s="1">
-        <v>1.7</v>
-      </c>
-      <c r="L18" s="1">
-        <v>85.3706</v>
-      </c>
-      <c r="M18" t="s">
-        <v>106</v>
-      </c>
-      <c r="N18">
+        <v>85.371</v>
+      </c>
+      <c r="L18" t="s">
+        <v>105</v>
+      </c>
+      <c r="M18">
         <v>0</v>
       </c>
-      <c r="O18" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15">
+      <c r="N18" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
       <c r="A19" s="3">
         <v>46226</v>
       </c>
       <c r="B19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D19" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E19" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F19">
         <v>44.7</v>
       </c>
       <c r="G19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H19">
-        <v>1.588</v>
+        <v>1.608</v>
       </c>
       <c r="I19" s="1">
-        <v>1.608</v>
+        <v>71.878</v>
       </c>
       <c r="J19">
-        <v>71.8776</v>
+        <v>1.7</v>
       </c>
       <c r="K19" s="1">
-        <v>1.7</v>
-      </c>
-      <c r="L19" s="1">
         <v>75.98999999999999</v>
       </c>
-      <c r="M19" t="s">
-        <v>107</v>
-      </c>
-      <c r="N19">
+      <c r="L19" t="s">
+        <v>106</v>
+      </c>
+      <c r="M19">
         <v>0</v>
       </c>
-      <c r="O19" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15">
+      <c r="N19" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
       <c r="A20" s="3">
         <v>46226</v>
       </c>
       <c r="B20" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D20" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E20" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F20">
         <v>1</v>
       </c>
       <c r="G20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H20">
         <v>8.289999999999999</v>
@@ -1937,87 +1877,81 @@
       <c r="K20" s="1">
         <v>8.289999999999999</v>
       </c>
-      <c r="L20" s="1">
-        <v>8.289999999999999</v>
-      </c>
-      <c r="M20" t="s">
-        <v>107</v>
-      </c>
-      <c r="N20">
+      <c r="L20" t="s">
+        <v>106</v>
+      </c>
+      <c r="M20">
         <v>0</v>
       </c>
-      <c r="O20" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15">
+      <c r="N20" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
       <c r="A21" s="3">
         <v>46226</v>
       </c>
       <c r="B21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C21" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D21" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E21" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F21">
         <v>47.006</v>
       </c>
       <c r="G21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H21">
-        <v>1.588</v>
+        <v>1.608</v>
       </c>
       <c r="I21" s="1">
-        <v>1.608</v>
+        <v>75.586</v>
       </c>
       <c r="J21">
-        <v>75.58564800000001</v>
+        <v>1.7</v>
       </c>
       <c r="K21" s="1">
-        <v>1.7</v>
-      </c>
-      <c r="L21" s="1">
-        <v>79.9102</v>
-      </c>
-      <c r="M21" t="s">
-        <v>108</v>
-      </c>
-      <c r="N21">
+        <v>79.91</v>
+      </c>
+      <c r="L21" t="s">
+        <v>107</v>
+      </c>
+      <c r="M21">
         <v>238910</v>
       </c>
-      <c r="O21" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15">
+      <c r="N21" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
       <c r="A22" s="3">
         <v>46226</v>
       </c>
       <c r="B22" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C22" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D22" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E22" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F22">
         <v>1</v>
       </c>
       <c r="G22" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H22">
         <v>4.49</v>
@@ -2031,463 +1965,433 @@
       <c r="K22" s="1">
         <v>4.49</v>
       </c>
-      <c r="L22" s="1">
-        <v>4.49</v>
-      </c>
-      <c r="M22" t="s">
-        <v>108</v>
-      </c>
-      <c r="N22">
+      <c r="L22" t="s">
+        <v>107</v>
+      </c>
+      <c r="M22">
         <v>238910</v>
       </c>
-      <c r="O22" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15">
+      <c r="N22" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
       <c r="A23" s="3">
         <v>46227</v>
       </c>
       <c r="B23" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C23" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D23" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F23">
         <v>59</v>
       </c>
       <c r="G23" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H23">
-        <v>1.619</v>
+        <v>1.639</v>
       </c>
       <c r="I23" s="1">
-        <v>1.639</v>
+        <v>96.70099999999999</v>
       </c>
       <c r="J23">
-        <v>96.70099999999999</v>
+        <v>1.7</v>
       </c>
       <c r="K23" s="1">
-        <v>1.7</v>
-      </c>
-      <c r="L23" s="1">
         <v>100.3</v>
       </c>
-      <c r="M23" t="s">
-        <v>109</v>
-      </c>
-      <c r="N23">
+      <c r="L23" t="s">
+        <v>108</v>
+      </c>
+      <c r="M23">
         <v>391012</v>
       </c>
-      <c r="O23" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15">
+      <c r="N23" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
       <c r="A24" s="3">
         <v>46227</v>
       </c>
       <c r="B24" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C24" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D24" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E24" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F24">
         <v>45.179</v>
       </c>
       <c r="G24" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H24">
-        <v>1.619</v>
+        <v>1.639</v>
       </c>
       <c r="I24" s="1">
-        <v>1.639</v>
+        <v>74.048</v>
       </c>
       <c r="J24">
-        <v>74.04838100000001</v>
+        <v>1.73</v>
       </c>
       <c r="K24" s="1">
-        <v>1.73</v>
-      </c>
-      <c r="L24" s="1">
-        <v>78.15967000000001</v>
-      </c>
-      <c r="M24" t="s">
-        <v>110</v>
-      </c>
-      <c r="N24">
+        <v>78.16</v>
+      </c>
+      <c r="L24" t="s">
+        <v>109</v>
+      </c>
+      <c r="M24">
         <v>49388</v>
       </c>
-      <c r="O24" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15">
+      <c r="N24" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
       <c r="A25" s="3">
         <v>46227</v>
       </c>
       <c r="B25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C25" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D25" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E25" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F25">
         <v>56.308</v>
       </c>
       <c r="G25" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H25">
-        <v>1.619</v>
+        <v>1.639</v>
       </c>
       <c r="I25" s="1">
-        <v>1.639</v>
+        <v>92.289</v>
       </c>
       <c r="J25">
-        <v>92.28881199999999</v>
+        <v>1.72</v>
       </c>
       <c r="K25" s="1">
-        <v>1.72</v>
-      </c>
-      <c r="L25" s="1">
-        <v>96.84976</v>
-      </c>
-      <c r="M25" t="s">
-        <v>111</v>
-      </c>
-      <c r="N25">
+        <v>96.84999999999999</v>
+      </c>
+      <c r="L25" t="s">
+        <v>110</v>
+      </c>
+      <c r="M25">
         <v>0</v>
       </c>
-      <c r="O25" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15">
+      <c r="N25" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
       <c r="A26" s="3">
         <v>46230</v>
       </c>
       <c r="B26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C26" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D26" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E26" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F26">
         <v>45</v>
       </c>
       <c r="G26" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H26">
-        <v>1.619</v>
+        <v>1.639</v>
       </c>
       <c r="I26" s="1">
-        <v>1.639</v>
+        <v>73.755</v>
       </c>
       <c r="J26">
-        <v>73.755</v>
+        <v>1.74</v>
       </c>
       <c r="K26" s="1">
-        <v>1.74</v>
-      </c>
-      <c r="L26" s="1">
         <v>78.3</v>
       </c>
-      <c r="M26" t="s">
-        <v>112</v>
-      </c>
-      <c r="N26">
+      <c r="L26" t="s">
+        <v>111</v>
+      </c>
+      <c r="M26">
         <v>0</v>
       </c>
-      <c r="O26" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15">
+      <c r="N26" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
       <c r="A27" s="3">
         <v>46230</v>
       </c>
       <c r="B27" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C27" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D27" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E27" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F27">
         <v>48.42</v>
       </c>
       <c r="G27" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H27">
-        <v>1.619</v>
+        <v>1.639</v>
       </c>
       <c r="I27" s="1">
-        <v>1.639</v>
+        <v>79.36</v>
       </c>
       <c r="J27">
-        <v>79.36038000000001</v>
+        <v>1.74</v>
       </c>
       <c r="K27" s="1">
-        <v>1.74</v>
-      </c>
-      <c r="L27" s="1">
-        <v>84.2508</v>
-      </c>
-      <c r="M27" t="s">
-        <v>113</v>
-      </c>
-      <c r="N27">
+        <v>84.251</v>
+      </c>
+      <c r="L27" t="s">
+        <v>112</v>
+      </c>
+      <c r="M27">
         <v>0</v>
       </c>
-      <c r="O27" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15">
+      <c r="N27" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
       <c r="A28" s="3">
         <v>46230</v>
       </c>
       <c r="B28" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C28" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D28" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E28" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F28">
         <v>40</v>
       </c>
       <c r="G28" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H28">
-        <v>1.619</v>
+        <v>1.639</v>
       </c>
       <c r="I28" s="1">
-        <v>1.639</v>
+        <v>65.56</v>
       </c>
       <c r="J28">
-        <v>65.56</v>
+        <v>1.75</v>
       </c>
       <c r="K28" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L28" s="1">
         <v>70</v>
       </c>
-      <c r="M28" t="s">
-        <v>114</v>
-      </c>
-      <c r="N28">
+      <c r="L28" t="s">
+        <v>113</v>
+      </c>
+      <c r="M28">
         <v>147973</v>
       </c>
-      <c r="O28" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15">
+      <c r="N28" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
       <c r="A29" s="3">
         <v>46230</v>
       </c>
       <c r="B29" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C29" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D29" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E29" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F29">
         <v>39.04</v>
       </c>
       <c r="G29" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H29">
-        <v>1.619</v>
+        <v>1.639</v>
       </c>
       <c r="I29" s="1">
-        <v>1.639</v>
+        <v>63.987</v>
       </c>
       <c r="J29">
-        <v>63.98656</v>
+        <v>1.76</v>
       </c>
       <c r="K29" s="1">
-        <v>1.76</v>
-      </c>
-      <c r="L29" s="1">
-        <v>68.71040000000001</v>
-      </c>
-      <c r="M29" t="s">
-        <v>115</v>
-      </c>
-      <c r="N29">
+        <v>68.70999999999999</v>
+      </c>
+      <c r="L29" t="s">
+        <v>114</v>
+      </c>
+      <c r="M29">
         <v>0</v>
       </c>
-      <c r="O29" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15">
+      <c r="N29" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
       <c r="A30" s="3">
         <v>46230</v>
       </c>
       <c r="B30" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C30" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E30" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F30">
         <v>40</v>
       </c>
       <c r="G30" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H30">
-        <v>1.619</v>
+        <v>1.639</v>
       </c>
       <c r="I30" s="1">
-        <v>1.639</v>
+        <v>65.56</v>
       </c>
       <c r="J30">
-        <v>65.56</v>
+        <v>1.75</v>
       </c>
       <c r="K30" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L30" s="1">
         <v>70</v>
       </c>
-      <c r="M30" t="s">
-        <v>116</v>
-      </c>
-      <c r="N30">
+      <c r="L30" t="s">
+        <v>115</v>
+      </c>
+      <c r="M30">
         <v>417017</v>
       </c>
-      <c r="O30" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15">
+      <c r="N30" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
       <c r="A31" s="3">
         <v>46231</v>
       </c>
       <c r="B31" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C31" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D31" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E31" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F31">
         <v>51</v>
       </c>
       <c r="G31" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H31">
-        <v>1.653</v>
+        <v>1.673</v>
       </c>
       <c r="I31" s="1">
-        <v>1.673</v>
+        <v>85.32299999999999</v>
       </c>
       <c r="J31">
-        <v>85.32299999999999</v>
+        <v>1.74</v>
       </c>
       <c r="K31" s="1">
-        <v>1.74</v>
-      </c>
-      <c r="L31" s="1">
         <v>88.73999999999999</v>
       </c>
-      <c r="M31" t="s">
-        <v>117</v>
-      </c>
-      <c r="N31">
+      <c r="L31" t="s">
+        <v>116</v>
+      </c>
+      <c r="M31">
         <v>471251</v>
       </c>
-      <c r="O31" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15">
+      <c r="N31" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
       <c r="A32" s="3">
         <v>46231</v>
       </c>
       <c r="B32" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C32" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D32" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E32" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F32">
         <v>1</v>
       </c>
       <c r="G32" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H32">
         <v>4.99</v>
@@ -2501,651 +2405,609 @@
       <c r="K32" s="1">
         <v>4.99</v>
       </c>
-      <c r="L32" s="1">
-        <v>4.99</v>
-      </c>
-      <c r="M32" t="s">
-        <v>117</v>
-      </c>
-      <c r="N32">
+      <c r="L32" t="s">
+        <v>116</v>
+      </c>
+      <c r="M32">
         <v>471251</v>
       </c>
-      <c r="O32" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15">
+      <c r="N32" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14">
       <c r="A33" s="3">
         <v>46231</v>
       </c>
       <c r="B33" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C33" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D33" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E33" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F33">
         <v>37</v>
       </c>
       <c r="G33" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H33">
-        <v>1.653</v>
+        <v>1.673</v>
       </c>
       <c r="I33" s="1">
-        <v>1.673</v>
+        <v>61.901</v>
       </c>
       <c r="J33">
-        <v>61.901</v>
+        <v>1.75</v>
       </c>
       <c r="K33" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L33" s="1">
         <v>64.75</v>
       </c>
-      <c r="M33" t="s">
-        <v>118</v>
-      </c>
-      <c r="N33">
+      <c r="L33" t="s">
+        <v>117</v>
+      </c>
+      <c r="M33">
         <v>0</v>
       </c>
-      <c r="O33" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15">
+      <c r="N33" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14">
       <c r="A34" s="3">
         <v>46232</v>
       </c>
       <c r="B34" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C34" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D34" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E34" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F34">
         <v>26.703</v>
       </c>
       <c r="G34" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H34">
-        <v>1.674</v>
+        <v>1.694</v>
       </c>
       <c r="I34" s="1">
-        <v>1.694</v>
+        <v>45.235</v>
       </c>
       <c r="J34">
-        <v>45.234882</v>
+        <v>1.75</v>
       </c>
       <c r="K34" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L34" s="1">
-        <v>46.73025</v>
-      </c>
-      <c r="M34" t="s">
-        <v>119</v>
-      </c>
-      <c r="N34">
+        <v>46.73</v>
+      </c>
+      <c r="L34" t="s">
+        <v>118</v>
+      </c>
+      <c r="M34">
         <v>0</v>
       </c>
-      <c r="O34" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15">
+      <c r="N34" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14">
       <c r="A35" s="3">
         <v>46232</v>
       </c>
       <c r="B35" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C35" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D35" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E35" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F35">
         <v>39.84</v>
       </c>
       <c r="G35" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H35">
-        <v>1.674</v>
+        <v>1.694</v>
       </c>
       <c r="I35" s="1">
-        <v>1.694</v>
+        <v>67.489</v>
       </c>
       <c r="J35">
-        <v>67.48896000000001</v>
+        <v>1.75</v>
       </c>
       <c r="K35" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L35" s="1">
         <v>69.72</v>
       </c>
-      <c r="M35" t="s">
-        <v>120</v>
-      </c>
-      <c r="N35">
+      <c r="L35" t="s">
+        <v>119</v>
+      </c>
+      <c r="M35">
         <v>339177</v>
       </c>
-      <c r="O35" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15">
+      <c r="N35" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14">
       <c r="A36" s="3">
         <v>46232</v>
       </c>
       <c r="B36" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C36" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D36" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E36" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F36">
         <v>55.88</v>
       </c>
       <c r="G36" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H36">
-        <v>1.674</v>
+        <v>1.694</v>
       </c>
       <c r="I36" s="1">
-        <v>1.694</v>
+        <v>94.661</v>
       </c>
       <c r="J36">
-        <v>94.66072</v>
+        <v>1.75</v>
       </c>
       <c r="K36" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L36" s="1">
         <v>97.79000000000001</v>
       </c>
-      <c r="M36" t="s">
-        <v>121</v>
-      </c>
-      <c r="N36">
+      <c r="L36" t="s">
+        <v>120</v>
+      </c>
+      <c r="M36">
         <v>0</v>
       </c>
-      <c r="O36" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15">
+      <c r="N36" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14">
       <c r="A37" s="3">
         <v>46233</v>
       </c>
       <c r="B37" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C37" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D37" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E37" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F37">
         <v>42.21</v>
       </c>
       <c r="G37" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H37">
-        <v>1.674</v>
+        <v>1.694</v>
       </c>
       <c r="I37" s="1">
-        <v>1.694</v>
+        <v>71.504</v>
       </c>
       <c r="J37">
-        <v>71.50373999999999</v>
+        <v>1.76</v>
       </c>
       <c r="K37" s="1">
-        <v>1.76</v>
-      </c>
-      <c r="L37" s="1">
-        <v>74.28959999999999</v>
-      </c>
-      <c r="M37" t="s">
-        <v>122</v>
-      </c>
-      <c r="N37">
+        <v>74.29000000000001</v>
+      </c>
+      <c r="L37" t="s">
+        <v>121</v>
+      </c>
+      <c r="M37">
         <v>229700</v>
       </c>
-      <c r="O37" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15">
+      <c r="N37" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14">
       <c r="A38" s="3">
         <v>46233</v>
       </c>
       <c r="B38" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C38" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D38" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E38" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F38">
         <v>40.817</v>
       </c>
       <c r="G38" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H38">
         <v>2.02</v>
       </c>
       <c r="I38" s="1">
+        <v>82.45</v>
+      </c>
+      <c r="J38">
         <v>2.02</v>
       </c>
-      <c r="J38">
-        <v>82.45034</v>
-      </c>
       <c r="K38" s="1">
-        <v>2.02</v>
-      </c>
-      <c r="L38" s="1">
-        <v>82.45034</v>
-      </c>
-      <c r="M38" t="s">
-        <v>123</v>
-      </c>
-      <c r="N38">
+        <v>82.45</v>
+      </c>
+      <c r="L38" t="s">
+        <v>122</v>
+      </c>
+      <c r="M38">
         <v>14825</v>
       </c>
-      <c r="O38" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15">
+      <c r="N38" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14">
       <c r="A39" s="3">
         <v>46233</v>
       </c>
       <c r="B39" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C39" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D39" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E39" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F39">
         <v>44</v>
       </c>
       <c r="G39" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H39">
-        <v>1.449</v>
+        <v>1.469</v>
       </c>
       <c r="I39" s="1">
-        <v>1.469</v>
+        <v>64.636</v>
       </c>
       <c r="J39">
-        <v>64.636</v>
+        <v>1.55</v>
       </c>
       <c r="K39" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="L39" s="1">
         <v>68.2</v>
       </c>
-      <c r="M39" t="s">
-        <v>124</v>
-      </c>
-      <c r="N39">
+      <c r="L39" t="s">
+        <v>123</v>
+      </c>
+      <c r="M39">
         <v>0</v>
       </c>
-      <c r="O39" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15">
+      <c r="N39" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14">
       <c r="A40" s="3">
         <v>46233</v>
       </c>
       <c r="B40" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C40" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D40" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E40" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F40">
         <v>43.358</v>
       </c>
       <c r="G40" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H40">
-        <v>1.674</v>
+        <v>1.694</v>
       </c>
       <c r="I40" s="1">
-        <v>1.694</v>
+        <v>73.44799999999999</v>
       </c>
       <c r="J40">
-        <v>73.448452</v>
+        <v>1.76</v>
       </c>
       <c r="K40" s="1">
-        <v>1.76</v>
-      </c>
-      <c r="L40" s="1">
-        <v>76.31008</v>
-      </c>
-      <c r="M40" t="s">
-        <v>125</v>
-      </c>
-      <c r="N40">
+        <v>76.31</v>
+      </c>
+      <c r="L40" t="s">
+        <v>124</v>
+      </c>
+      <c r="M40">
         <v>0</v>
       </c>
-      <c r="O40" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15">
+      <c r="N40" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14">
       <c r="A41" s="3">
         <v>46233</v>
       </c>
       <c r="B41" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C41" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D41" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E41" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F41">
         <v>18.182</v>
       </c>
       <c r="G41" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H41">
-        <v>1.674</v>
+        <v>1.694</v>
       </c>
       <c r="I41" s="1">
-        <v>1.694</v>
+        <v>30.8</v>
       </c>
       <c r="J41">
-        <v>30.800308</v>
+        <v>1.76</v>
       </c>
       <c r="K41" s="1">
-        <v>1.76</v>
-      </c>
-      <c r="L41" s="1">
-        <v>32.00032</v>
-      </c>
-      <c r="M41" t="s">
-        <v>126</v>
-      </c>
-      <c r="N41">
+        <v>32</v>
+      </c>
+      <c r="L41" t="s">
+        <v>125</v>
+      </c>
+      <c r="M41">
         <v>393583</v>
       </c>
-      <c r="O41" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15">
+      <c r="N41" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14">
       <c r="A42" s="3">
         <v>46234</v>
       </c>
       <c r="B42" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C42" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D42" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E42" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F42">
         <v>35</v>
       </c>
       <c r="G42" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H42">
-        <v>1.689</v>
+        <v>1.709</v>
       </c>
       <c r="I42" s="1">
-        <v>1.709</v>
+        <v>59.815</v>
       </c>
       <c r="J42">
-        <v>59.815</v>
+        <v>1.77</v>
       </c>
       <c r="K42" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L42" s="1">
         <v>61.95</v>
       </c>
-      <c r="M42" t="s">
-        <v>127</v>
-      </c>
-      <c r="N42">
+      <c r="L42" t="s">
+        <v>126</v>
+      </c>
+      <c r="M42">
         <v>471900</v>
       </c>
-      <c r="O42" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="43" spans="1:15">
+      <c r="N42" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14">
       <c r="A43" s="3">
         <v>46234</v>
       </c>
       <c r="B43" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C43" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D43" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E43" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F43">
         <v>42</v>
       </c>
       <c r="G43" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H43">
-        <v>1.689</v>
+        <v>1.709</v>
       </c>
       <c r="I43" s="1">
-        <v>1.709</v>
+        <v>71.77800000000001</v>
       </c>
       <c r="J43">
-        <v>71.77800000000001</v>
+        <v>1.77</v>
       </c>
       <c r="K43" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L43" s="1">
         <v>74.34</v>
       </c>
-      <c r="M43" t="s">
-        <v>128</v>
-      </c>
-      <c r="N43">
+      <c r="L43" t="s">
+        <v>127</v>
+      </c>
+      <c r="M43">
         <v>0</v>
       </c>
-      <c r="O43" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15">
+      <c r="N43" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14">
       <c r="A44" s="3">
         <v>46234</v>
       </c>
       <c r="B44" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C44" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D44" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E44" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F44">
         <v>12</v>
       </c>
       <c r="G44" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H44">
-        <v>1.689</v>
+        <v>1.709</v>
       </c>
       <c r="I44" s="1">
-        <v>1.709</v>
+        <v>20.508</v>
       </c>
       <c r="J44">
-        <v>20.508</v>
+        <v>1.77</v>
       </c>
       <c r="K44" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L44" s="1">
         <v>21.24</v>
       </c>
-      <c r="M44" t="s">
-        <v>129</v>
-      </c>
-      <c r="N44">
+      <c r="L44" t="s">
+        <v>128</v>
+      </c>
+      <c r="M44">
         <v>0</v>
       </c>
-      <c r="O44" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="45" spans="1:15">
+      <c r="N44" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14">
       <c r="A45" s="3">
         <v>46234</v>
       </c>
       <c r="B45" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C45" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D45" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E45" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F45">
         <v>41.299</v>
       </c>
       <c r="G45" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H45">
-        <v>1.689</v>
+        <v>1.709</v>
       </c>
       <c r="I45" s="1">
-        <v>1.709</v>
+        <v>70.58</v>
       </c>
       <c r="J45">
-        <v>70.57999100000001</v>
+        <v>1.77</v>
       </c>
       <c r="K45" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L45" s="1">
-        <v>73.09923000000001</v>
-      </c>
-      <c r="M45" t="s">
-        <v>130</v>
-      </c>
-      <c r="N45">
+        <v>73.099</v>
+      </c>
+      <c r="L45" t="s">
+        <v>129</v>
+      </c>
+      <c r="M45">
         <v>0</v>
       </c>
-      <c r="O45" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15">
+      <c r="N45" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14">
       <c r="A46" s="3">
         <v>46234</v>
       </c>
       <c r="B46" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C46" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D46" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E46" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F46">
         <v>1</v>
       </c>
       <c r="G46" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H46">
         <v>3.52</v>
@@ -3159,40 +3021,37 @@
       <c r="K46" s="1">
         <v>3.52</v>
       </c>
-      <c r="L46" s="1">
-        <v>3.52</v>
-      </c>
-      <c r="M46" t="s">
-        <v>130</v>
-      </c>
-      <c r="N46">
+      <c r="L46" t="s">
+        <v>129</v>
+      </c>
+      <c r="M46">
         <v>0</v>
       </c>
-      <c r="O46" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="47" spans="1:15">
+      <c r="N46" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14">
       <c r="A47" s="3">
         <v>46234</v>
       </c>
       <c r="B47" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C47" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D47" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E47" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F47">
         <v>1</v>
       </c>
       <c r="G47" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H47">
         <v>9.390000000000001</v>
@@ -3206,398 +3065,371 @@
       <c r="K47" s="1">
         <v>9.390000000000001</v>
       </c>
-      <c r="L47" s="1">
-        <v>9.390000000000001</v>
-      </c>
-      <c r="M47" t="s">
-        <v>130</v>
-      </c>
-      <c r="N47">
+      <c r="L47" t="s">
+        <v>129</v>
+      </c>
+      <c r="M47">
         <v>0</v>
       </c>
-      <c r="O47" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="48" spans="1:15">
+      <c r="N47" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14">
       <c r="A48" s="3">
         <v>46234</v>
       </c>
       <c r="B48" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C48" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D48" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E48" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F48">
         <v>49.497</v>
       </c>
       <c r="G48" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H48">
-        <v>1.689</v>
+        <v>1.709</v>
       </c>
       <c r="I48" s="1">
-        <v>1.709</v>
+        <v>84.59</v>
       </c>
       <c r="J48">
-        <v>84.590373</v>
+        <v>1.77</v>
       </c>
       <c r="K48" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L48" s="1">
-        <v>87.60969</v>
-      </c>
-      <c r="M48" t="s">
-        <v>131</v>
-      </c>
-      <c r="N48">
+        <v>87.61</v>
+      </c>
+      <c r="L48" t="s">
+        <v>130</v>
+      </c>
+      <c r="M48">
         <v>239890</v>
       </c>
-      <c r="O48" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="49" spans="1:15">
+      <c r="N48" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14">
       <c r="A49" s="3">
         <v>46234</v>
       </c>
       <c r="B49" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C49" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D49" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E49" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F49">
         <v>35</v>
       </c>
       <c r="G49" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H49">
-        <v>1.689</v>
+        <v>1.709</v>
       </c>
       <c r="I49" s="1">
-        <v>1.709</v>
+        <v>59.815</v>
       </c>
       <c r="J49">
-        <v>59.815</v>
+        <v>1.76</v>
       </c>
       <c r="K49" s="1">
-        <v>1.76</v>
-      </c>
-      <c r="L49" s="1">
         <v>61.6</v>
       </c>
-      <c r="M49" t="s">
-        <v>132</v>
-      </c>
-      <c r="N49">
+      <c r="L49" t="s">
+        <v>131</v>
+      </c>
+      <c r="M49">
         <v>576900</v>
       </c>
-      <c r="O49" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="50" spans="1:15">
+      <c r="N49" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14">
       <c r="A50" s="3">
         <v>46234</v>
       </c>
       <c r="B50" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C50" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D50" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E50" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F50">
         <v>42</v>
       </c>
       <c r="G50" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H50">
-        <v>1.689</v>
+        <v>1.709</v>
       </c>
       <c r="I50" s="1">
-        <v>1.709</v>
+        <v>71.77800000000001</v>
       </c>
       <c r="J50">
-        <v>71.77800000000001</v>
+        <v>1.78</v>
       </c>
       <c r="K50" s="1">
-        <v>1.78</v>
-      </c>
-      <c r="L50" s="1">
         <v>74.76000000000001</v>
       </c>
-      <c r="M50" t="s">
-        <v>133</v>
-      </c>
-      <c r="N50">
+      <c r="L50" t="s">
+        <v>132</v>
+      </c>
+      <c r="M50">
         <v>176276</v>
       </c>
-      <c r="O50" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="51" spans="1:15">
+      <c r="N50" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14">
       <c r="A51" s="3">
         <v>46234</v>
       </c>
       <c r="B51" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C51" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D51" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E51" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F51">
         <v>48.599</v>
       </c>
       <c r="G51" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H51">
-        <v>1.689</v>
+        <v>1.709</v>
       </c>
       <c r="I51" s="1">
-        <v>1.709</v>
+        <v>83.056</v>
       </c>
       <c r="J51">
-        <v>83.055691</v>
+        <v>1.77</v>
       </c>
       <c r="K51" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L51" s="1">
-        <v>86.02023</v>
-      </c>
-      <c r="M51" t="s">
-        <v>134</v>
-      </c>
-      <c r="N51">
+        <v>86.02</v>
+      </c>
+      <c r="L51" t="s">
+        <v>133</v>
+      </c>
+      <c r="M51">
         <v>0</v>
       </c>
-      <c r="O51" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="52" spans="1:15">
+      <c r="N51" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14">
       <c r="A52" s="3">
         <v>46234</v>
       </c>
       <c r="B52" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C52" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D52" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E52" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F52">
         <v>39.672</v>
       </c>
       <c r="G52" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H52">
-        <v>1.689</v>
+        <v>1.709</v>
       </c>
       <c r="I52" s="1">
-        <v>1.709</v>
+        <v>67.79900000000001</v>
       </c>
       <c r="J52">
-        <v>67.799448</v>
+        <v>1.77</v>
       </c>
       <c r="K52" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L52" s="1">
-        <v>70.21944000000001</v>
-      </c>
-      <c r="M52" t="s">
-        <v>135</v>
-      </c>
-      <c r="N52">
+        <v>70.21899999999999</v>
+      </c>
+      <c r="L52" t="s">
+        <v>134</v>
+      </c>
+      <c r="M52">
         <v>165568</v>
       </c>
-      <c r="O52" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="53" spans="1:15">
+      <c r="N52" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14">
       <c r="A53" s="3">
         <v>46234</v>
       </c>
       <c r="B53" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C53" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D53" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E53" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F53">
         <v>12.65</v>
       </c>
       <c r="G53" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H53">
-        <v>1.689</v>
+        <v>1.709</v>
       </c>
       <c r="I53" s="1">
-        <v>1.709</v>
+        <v>21.619</v>
       </c>
       <c r="J53">
-        <v>21.61885</v>
+        <v>1.77</v>
       </c>
       <c r="K53" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L53" s="1">
-        <v>22.3905</v>
-      </c>
-      <c r="M53" t="s">
-        <v>136</v>
-      </c>
-      <c r="N53">
+        <v>22.39</v>
+      </c>
+      <c r="L53" t="s">
+        <v>135</v>
+      </c>
+      <c r="M53">
         <v>165960</v>
       </c>
-      <c r="O53" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="54" spans="1:15">
+      <c r="N53" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14">
       <c r="A54" s="3">
         <v>46234</v>
       </c>
       <c r="B54" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C54" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D54" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E54" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F54">
         <v>47.23</v>
       </c>
       <c r="G54" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H54">
-        <v>1.689</v>
+        <v>1.709</v>
       </c>
       <c r="I54" s="1">
-        <v>1.709</v>
+        <v>80.71599999999999</v>
       </c>
       <c r="J54">
-        <v>80.71607</v>
+        <v>1.78</v>
       </c>
       <c r="K54" s="1">
-        <v>1.78</v>
-      </c>
-      <c r="L54" s="1">
-        <v>84.0694</v>
-      </c>
-      <c r="M54" t="s">
-        <v>105</v>
-      </c>
-      <c r="N54">
+        <v>84.069</v>
+      </c>
+      <c r="L54" t="s">
+        <v>104</v>
+      </c>
+      <c r="M54">
         <v>421577</v>
       </c>
-      <c r="O54" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="55" spans="1:15">
+      <c r="N54" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14">
       <c r="A55" s="3">
         <v>46234</v>
       </c>
       <c r="B55" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C55" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D55" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E55" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F55">
         <v>20.011</v>
       </c>
       <c r="G55" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H55">
-        <v>1.689</v>
+        <v>1.709</v>
       </c>
       <c r="I55" s="1">
-        <v>1.709</v>
+        <v>34.199</v>
       </c>
       <c r="J55">
-        <v>34.198799</v>
+        <v>1.78</v>
       </c>
       <c r="K55" s="1">
-        <v>1.78</v>
-      </c>
-      <c r="L55" s="1">
-        <v>35.61958</v>
-      </c>
-      <c r="M55" t="s">
-        <v>137</v>
-      </c>
-      <c r="N55">
+        <v>35.62</v>
+      </c>
+      <c r="L55" t="s">
+        <v>136</v>
+      </c>
+      <c r="M55">
         <v>0</v>
       </c>
-      <c r="O55" t="s">
+      <c r="N55" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14">
+      <c r="A58" s="4" t="s">
         <v>185</v>
-      </c>
-    </row>
-    <row r="58" spans="1:15">
-      <c r="A58" s="4" t="s">
-        <v>186</v>
       </c>
       <c r="B58" s="4"/>
       <c r="C58" s="4"/>
@@ -3605,189 +3437,189 @@
       <c r="E58" s="4"/>
       <c r="F58" s="4"/>
     </row>
-    <row r="59" spans="1:15">
+    <row r="59" spans="1:14">
       <c r="A59" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="B59" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="B59" s="5" t="s">
+      <c r="C59" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="C59" s="5" t="s">
+      <c r="D59" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="D59" s="5" t="s">
-        <v>190</v>
-      </c>
       <c r="E59" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="60" spans="1:15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14">
       <c r="A60" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B60" s="7">
         <v>1994.159</v>
       </c>
-      <c r="C60" s="7">
+      <c r="C60" s="8">
         <v>46</v>
       </c>
       <c r="D60" s="8">
-        <v>1.633079</v>
-      </c>
-      <c r="E60" s="7">
+        <v>1.633</v>
+      </c>
+      <c r="E60" s="8">
         <v>3256.62</v>
       </c>
-      <c r="F60" s="7">
-        <v>3422.75</v>
-      </c>
-    </row>
-    <row r="61" spans="1:15">
+      <c r="F60" s="8">
+        <v>3422.752</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14">
       <c r="A61" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B61" s="7">
         <v>44</v>
       </c>
-      <c r="C61" s="7">
+      <c r="C61" s="8">
         <v>1</v>
       </c>
       <c r="D61" s="8">
         <v>1.469</v>
       </c>
-      <c r="E61" s="7">
-        <v>64.64</v>
-      </c>
-      <c r="F61" s="7">
+      <c r="E61" s="8">
+        <v>64.636</v>
+      </c>
+      <c r="F61" s="8">
         <v>68.2</v>
       </c>
     </row>
-    <row r="62" spans="1:15">
+    <row r="62" spans="1:14">
       <c r="A62" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B62" s="7">
         <v>40.817</v>
       </c>
-      <c r="C62" s="7">
+      <c r="C62" s="8">
         <v>1</v>
       </c>
       <c r="D62" s="8">
         <v>2.02</v>
       </c>
-      <c r="E62" s="7">
+      <c r="E62" s="8">
         <v>82.45</v>
       </c>
-      <c r="F62" s="7">
+      <c r="F62" s="8">
         <v>82.45</v>
       </c>
     </row>
-    <row r="63" spans="1:15">
+    <row r="63" spans="1:14">
       <c r="A63" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B63" s="7">
         <v>2</v>
       </c>
-      <c r="C63" s="7">
+      <c r="C63" s="8">
         <v>2</v>
       </c>
       <c r="D63" s="8">
         <v>4.74</v>
       </c>
-      <c r="E63" s="7">
+      <c r="E63" s="8">
         <v>9.48</v>
       </c>
-      <c r="F63" s="7">
+      <c r="F63" s="8">
         <v>9.48</v>
       </c>
     </row>
-    <row r="64" spans="1:15">
+    <row r="64" spans="1:14">
       <c r="A64" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B64" s="7">
         <v>1</v>
       </c>
-      <c r="C64" s="7">
+      <c r="C64" s="8">
         <v>1</v>
       </c>
       <c r="D64" s="8">
         <v>8.289999999999999</v>
       </c>
-      <c r="E64" s="7">
+      <c r="E64" s="8">
         <v>8.289999999999999</v>
       </c>
-      <c r="F64" s="7">
+      <c r="F64" s="8">
         <v>8.289999999999999</v>
       </c>
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B65" s="7">
         <v>1</v>
       </c>
-      <c r="C65" s="7">
+      <c r="C65" s="8">
         <v>1</v>
       </c>
       <c r="D65" s="8">
         <v>9.390000000000001</v>
       </c>
-      <c r="E65" s="7">
+      <c r="E65" s="8">
         <v>9.390000000000001</v>
       </c>
-      <c r="F65" s="7">
+      <c r="F65" s="8">
         <v>9.390000000000001</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B66" s="7">
         <v>1</v>
       </c>
-      <c r="C66" s="7">
+      <c r="C66" s="8">
         <v>1</v>
       </c>
       <c r="D66" s="8">
         <v>3.52</v>
       </c>
-      <c r="E66" s="7">
+      <c r="E66" s="8">
         <v>3.52</v>
       </c>
-      <c r="F66" s="7">
+      <c r="F66" s="8">
         <v>3.52</v>
       </c>
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B67" s="7">
         <v>1</v>
       </c>
-      <c r="C67" s="7">
+      <c r="C67" s="8">
         <v>1</v>
       </c>
       <c r="D67" s="8">
         <v>1.02</v>
       </c>
-      <c r="E67" s="7">
+      <c r="E67" s="8">
         <v>1.02</v>
       </c>
-      <c r="F67" s="7">
+      <c r="F67" s="8">
         <v>1.02</v>
       </c>
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B68" s="10">
         <v>2084.976</v>
@@ -3797,10 +3629,10 @@
       </c>
       <c r="D68" s="8"/>
       <c r="E68" s="10">
-        <v>3435.41</v>
+        <v>3435.406</v>
       </c>
       <c r="F68" s="10">
-        <v>3605.1</v>
+        <v>3605.102</v>
       </c>
     </row>
   </sheetData>
